--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -195,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
   <si>
     <t>0,0</t>
   </si>
@@ -577,6 +577,33 @@
   </si>
   <si>
     <t>laboratory5</t>
+  </si>
+  <si>
+    <t>ActionClassName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>HelloFacilityAction</t>
+  </si>
+  <si>
+    <t>drill1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DrillAction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1260,14 +1287,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:L29" totalsRowShown="0">
-  <autoFilter ref="A1:L29"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:M30" totalsRowShown="0">
+  <autoFilter ref="A1:M30"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="5" name="Name"/>
     <tableColumn id="2" name="DisplayName"/>
     <tableColumn id="8" name="Type"/>
     <tableColumn id="3" name="Level"/>
+    <tableColumn id="13" name="ActionClassName"/>
     <tableColumn id="11" name="BuildResourceId"/>
     <tableColumn id="12" name="BuildResourceCount"/>
     <tableColumn id="7" name="InputItemId"/>
@@ -1543,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.25" customWidth="1"/>
@@ -1555,7 +1583,7 @@
     <col min="12" max="12" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1572,28 +1600,31 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101011</v>
       </c>
@@ -1609,17 +1640,20 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="J2">
+      <c r="F2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2">
         <v>1001</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>101012</v>
       </c>
@@ -1635,17 +1669,20 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="J3">
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3">
         <v>1001</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>10</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>101013</v>
       </c>
@@ -1661,17 +1698,20 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="F4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4">
         <v>1001</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>100</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>101021</v>
       </c>
@@ -1687,23 +1727,26 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="F5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5">
         <v>1001</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1002</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>101022</v>
       </c>
@@ -1719,23 +1762,26 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="H6">
+      <c r="F6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6">
         <v>1001</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>1002</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>101023</v>
       </c>
@@ -1751,23 +1797,26 @@
       <c r="E7">
         <v>3</v>
       </c>
-      <c r="H7">
+      <c r="F7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7">
         <v>1001</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>100</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1002</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>100</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>102011</v>
       </c>
@@ -1783,17 +1832,20 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="J8">
+      <c r="F8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8">
         <v>1003</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>1</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>102012</v>
       </c>
@@ -1809,17 +1861,20 @@
       <c r="E9">
         <v>2</v>
       </c>
-      <c r="J9">
+      <c r="F9" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9">
         <v>1003</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>10</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>102013</v>
       </c>
@@ -1835,17 +1890,20 @@
       <c r="E10">
         <v>3</v>
       </c>
-      <c r="J10">
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10">
         <v>1003</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>100</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>102021</v>
       </c>
@@ -1861,23 +1919,26 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="H11">
+      <c r="F11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11">
         <v>1003</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1004</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>102022</v>
       </c>
@@ -1893,23 +1954,26 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="H12">
+      <c r="F12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12">
         <v>1003</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>10</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>1004</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>10</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>102023</v>
       </c>
@@ -1925,23 +1989,26 @@
       <c r="E13">
         <v>3</v>
       </c>
-      <c r="H13">
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13">
         <v>1003</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>100</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>1004</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>100</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>103011</v>
       </c>
@@ -1957,17 +2024,20 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="J14">
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14">
         <v>1005</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>103012</v>
       </c>
@@ -1983,17 +2053,20 @@
       <c r="E15">
         <v>2</v>
       </c>
-      <c r="J15">
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15">
         <v>1005</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>10</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>103013</v>
       </c>
@@ -2009,17 +2082,20 @@
       <c r="E16">
         <v>3</v>
       </c>
-      <c r="J16">
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16">
         <v>1005</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>100</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>103021</v>
       </c>
@@ -2035,23 +2111,26 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="H17">
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17">
         <v>1004</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>1</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1006</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>103022</v>
       </c>
@@ -2067,23 +2146,26 @@
       <c r="E18">
         <v>2</v>
       </c>
-      <c r="H18">
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18">
         <v>1004</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>10</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>1005</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>10</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>103023</v>
       </c>
@@ -2099,23 +2181,26 @@
       <c r="E19">
         <v>3</v>
       </c>
-      <c r="H19">
+      <c r="F19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19">
         <v>1004</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>100</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>1005</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>100</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>110001</v>
       </c>
@@ -2131,11 +2216,14 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="L20" t="s">
+      <c r="F20" t="s">
+        <v>79</v>
+      </c>
+      <c r="M20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>110002</v>
       </c>
@@ -2151,11 +2239,14 @@
       <c r="E21">
         <v>2</v>
       </c>
-      <c r="L21" t="s">
+      <c r="F21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>110003</v>
       </c>
@@ -2171,11 +2262,14 @@
       <c r="E22">
         <v>3</v>
       </c>
-      <c r="L22" t="s">
+      <c r="F22" t="s">
+        <v>79</v>
+      </c>
+      <c r="M22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>110004</v>
       </c>
@@ -2191,11 +2285,14 @@
       <c r="E23">
         <v>4</v>
       </c>
-      <c r="L23" t="s">
+      <c r="F23" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>110005</v>
       </c>
@@ -2211,11 +2308,14 @@
       <c r="E24">
         <v>5</v>
       </c>
-      <c r="L24" t="s">
+      <c r="F24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M24" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>111001</v>
       </c>
@@ -2231,11 +2331,14 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="L25" t="s">
+      <c r="F25" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>111002</v>
       </c>
@@ -2251,11 +2354,14 @@
       <c r="E26">
         <v>2</v>
       </c>
-      <c r="L26" t="s">
+      <c r="F26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>111003</v>
       </c>
@@ -2271,11 +2377,14 @@
       <c r="E27">
         <v>3</v>
       </c>
-      <c r="L27" t="s">
+      <c r="F27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>111004</v>
       </c>
@@ -2291,11 +2400,14 @@
       <c r="E28">
         <v>4</v>
       </c>
-      <c r="L28" t="s">
+      <c r="F28" t="s">
+        <v>79</v>
+      </c>
+      <c r="M28" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>111005</v>
       </c>
@@ -2311,8 +2423,34 @@
       <c r="E29">
         <v>5</v>
       </c>
-      <c r="L29" t="s">
+      <c r="F29" t="s">
+        <v>79</v>
+      </c>
+      <c r="M29" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>112001</v>
+      </c>
+      <c r="B30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
+      <c r="M30" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -315,10 +315,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Coordinate</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DisplayName</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -603,6 +599,10 @@
   </si>
   <si>
     <t>DrillAction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coordinates</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1302,7 +1302,7 @@
     <tableColumn id="10" name="InputItemCount"/>
     <tableColumn id="6" name="OutputItemId"/>
     <tableColumn id="9" name="OutputItemCount"/>
-    <tableColumn id="4" name="Coordinate"/>
+    <tableColumn id="4" name="Coordinates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1581,6 +1581,7 @@
     <col min="7" max="7" width="22.5" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="12" max="12" width="18.125" customWidth="1"/>
+    <col min="13" max="13" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1588,40 +1589,40 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" t="s">
         <v>47</v>
       </c>
-      <c r="H1" t="s">
-        <v>48</v>
-      </c>
       <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
       <c r="M1" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1629,19 +1630,19 @@
         <v>101011</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K2">
         <v>1001</v>
@@ -1658,19 +1659,19 @@
         <v>101012</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K3">
         <v>1001</v>
@@ -1679,7 +1680,7 @@
         <v>10</v>
       </c>
       <c r="M3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1687,19 +1688,19 @@
         <v>101013</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K4">
         <v>1001</v>
@@ -1708,7 +1709,7 @@
         <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1716,19 +1717,19 @@
         <v>101021</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I5">
         <v>1001</v>
@@ -1751,19 +1752,19 @@
         <v>101022</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I6">
         <v>1001</v>
@@ -1778,7 +1779,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1786,19 +1787,19 @@
         <v>101023</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I7">
         <v>1001</v>
@@ -1813,7 +1814,7 @@
         <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1821,19 +1822,19 @@
         <v>102011</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K8">
         <v>1003</v>
@@ -1850,19 +1851,19 @@
         <v>102012</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K9">
         <v>1003</v>
@@ -1871,7 +1872,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1879,19 +1880,19 @@
         <v>102013</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K10">
         <v>1003</v>
@@ -1900,7 +1901,7 @@
         <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1908,19 +1909,19 @@
         <v>102021</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I11">
         <v>1003</v>
@@ -1943,19 +1944,19 @@
         <v>102022</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I12">
         <v>1003</v>
@@ -1970,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1978,19 +1979,19 @@
         <v>102023</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I13">
         <v>1003</v>
@@ -2005,7 +2006,7 @@
         <v>100</v>
       </c>
       <c r="M13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -2013,19 +2014,19 @@
         <v>103011</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K14">
         <v>1005</v>
@@ -2042,19 +2043,19 @@
         <v>103012</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K15">
         <v>1005</v>
@@ -2063,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -2071,19 +2072,19 @@
         <v>103013</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K16">
         <v>1005</v>
@@ -2092,7 +2093,7 @@
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -2100,19 +2101,19 @@
         <v>103021</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I17">
         <v>1004</v>
@@ -2135,19 +2136,19 @@
         <v>103022</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I18">
         <v>1004</v>
@@ -2162,7 +2163,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -2170,19 +2171,19 @@
         <v>103023</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I19">
         <v>1004</v>
@@ -2197,7 +2198,7 @@
         <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -2205,22 +2206,22 @@
         <v>110001</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -2228,22 +2229,22 @@
         <v>110002</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -2251,22 +2252,22 @@
         <v>110003</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -2274,22 +2275,22 @@
         <v>110004</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23">
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -2297,22 +2298,22 @@
         <v>110005</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2320,22 +2321,22 @@
         <v>111001</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -2343,22 +2344,22 @@
         <v>111002</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -2366,22 +2367,22 @@
         <v>111003</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -2389,22 +2390,22 @@
         <v>111004</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -2412,22 +2413,22 @@
         <v>111005</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
         <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>71</v>
       </c>
       <c r="E29">
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -2435,22 +2436,22 @@
         <v>112001</v>
       </c>
       <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
         <v>80</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>82</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB60FED-5B5A-40EF-84CA-EC46D0B9B304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="9705"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -195,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -594,22 +595,22 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>0,0;0,1;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DrillAction</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Coordinates</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1287,22 +1288,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:M30" totalsRowShown="0">
-  <autoFilter ref="A1:M30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:M30" totalsRowShown="0">
+  <autoFilter ref="A1:M30" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="5" name="Name"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="8" name="Type"/>
-    <tableColumn id="3" name="Level"/>
-    <tableColumn id="13" name="ActionClassName"/>
-    <tableColumn id="11" name="BuildResourceId"/>
-    <tableColumn id="12" name="BuildResourceCount"/>
-    <tableColumn id="7" name="InputItemId"/>
-    <tableColumn id="10" name="InputItemCount"/>
-    <tableColumn id="6" name="OutputItemId"/>
-    <tableColumn id="9" name="OutputItemCount"/>
-    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ActionClassName"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1570,7 +1571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1622,7 +1623,7 @@
         <v>22</v>
       </c>
       <c r="M1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -2448,10 +2449,10 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB60FED-5B5A-40EF-84CA-EC46D0B9B304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -20,12 +19,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -303,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="101">
   <si>
     <t>0,0</t>
   </si>
@@ -604,13 +603,77 @@
   </si>
   <si>
     <t>0,0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구를 진행하여 공장을 강화할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 엔진을 개발하거나, 기존의 엔진들을 합성할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 광석을 철 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대 드릴을 작동하기 위한 모터 시설이다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1288,22 +1351,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:M30" totalsRowShown="0">
-  <autoFilter ref="A1:M30" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ActionClassName"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:N30" totalsRowShown="0">
+  <autoFilter ref="A1:N30"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="5" name="Name"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="8" name="Type"/>
+    <tableColumn id="3" name="Level"/>
+    <tableColumn id="13" name="ActionClassName"/>
+    <tableColumn id="15" name="Desc"/>
+    <tableColumn id="11" name="BuildResourceId"/>
+    <tableColumn id="12" name="BuildResourceCount"/>
+    <tableColumn id="7" name="InputItemId"/>
+    <tableColumn id="10" name="InputItemCount"/>
+    <tableColumn id="6" name="OutputItemId"/>
+    <tableColumn id="9" name="OutputItemCount"/>
+    <tableColumn id="4" name="Coordinates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1571,21 +1635,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.25" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="24.125" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="40.25" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="12" max="12" width="18.125" customWidth="1"/>
     <col min="13" max="13" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1605,28 +1669,31 @@
         <v>77</v>
       </c>
       <c r="G1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101011</v>
       </c>
@@ -1645,17 +1712,20 @@
       <c r="F2" t="s">
         <v>78</v>
       </c>
-      <c r="K2">
+      <c r="G2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2">
         <v>1001</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>101012</v>
       </c>
@@ -1674,17 +1744,20 @@
       <c r="F3" t="s">
         <v>78</v>
       </c>
-      <c r="K3">
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3">
         <v>1001</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>10</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>101013</v>
       </c>
@@ -1703,17 +1776,20 @@
       <c r="F4" t="s">
         <v>78</v>
       </c>
-      <c r="K4">
+      <c r="G4" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4">
         <v>1001</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>100</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>101021</v>
       </c>
@@ -1732,23 +1808,26 @@
       <c r="F5" t="s">
         <v>78</v>
       </c>
-      <c r="I5">
+      <c r="G5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5">
         <v>1001</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1002</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>101022</v>
       </c>
@@ -1767,23 +1846,26 @@
       <c r="F6" t="s">
         <v>78</v>
       </c>
-      <c r="I6">
+      <c r="G6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6">
         <v>1001</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>1002</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>101023</v>
       </c>
@@ -1802,23 +1884,26 @@
       <c r="F7" t="s">
         <v>78</v>
       </c>
-      <c r="I7">
+      <c r="G7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7">
         <v>1001</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>100</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1002</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>100</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>102011</v>
       </c>
@@ -1837,17 +1922,20 @@
       <c r="F8" t="s">
         <v>78</v>
       </c>
-      <c r="K8">
+      <c r="G8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8">
         <v>1003</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>102012</v>
       </c>
@@ -1866,17 +1954,20 @@
       <c r="F9" t="s">
         <v>78</v>
       </c>
-      <c r="K9">
+      <c r="G9" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9">
         <v>1003</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>10</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>102013</v>
       </c>
@@ -1895,17 +1986,20 @@
       <c r="F10" t="s">
         <v>78</v>
       </c>
-      <c r="K10">
+      <c r="G10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10">
         <v>1003</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>100</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>102021</v>
       </c>
@@ -1924,23 +2018,26 @@
       <c r="F11" t="s">
         <v>78</v>
       </c>
-      <c r="I11">
+      <c r="G11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11">
         <v>1003</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1004</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>102022</v>
       </c>
@@ -1959,23 +2056,26 @@
       <c r="F12" t="s">
         <v>78</v>
       </c>
-      <c r="I12">
+      <c r="G12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12">
         <v>1003</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>10</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>1004</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>10</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>102023</v>
       </c>
@@ -1994,23 +2094,26 @@
       <c r="F13" t="s">
         <v>78</v>
       </c>
-      <c r="I13">
+      <c r="G13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13">
         <v>1003</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>100</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>1004</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>100</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>103011</v>
       </c>
@@ -2029,17 +2132,20 @@
       <c r="F14" t="s">
         <v>78</v>
       </c>
-      <c r="K14">
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14">
         <v>1005</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>103012</v>
       </c>
@@ -2058,17 +2164,20 @@
       <c r="F15" t="s">
         <v>78</v>
       </c>
-      <c r="K15">
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15">
         <v>1005</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>10</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>103013</v>
       </c>
@@ -2087,17 +2196,20 @@
       <c r="F16" t="s">
         <v>78</v>
       </c>
-      <c r="K16">
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="L16">
         <v>1005</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>100</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>103021</v>
       </c>
@@ -2116,23 +2228,26 @@
       <c r="F17" t="s">
         <v>78</v>
       </c>
-      <c r="I17">
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="J17">
         <v>1004</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1006</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>1</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>103022</v>
       </c>
@@ -2151,23 +2266,26 @@
       <c r="F18" t="s">
         <v>78</v>
       </c>
-      <c r="I18">
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18">
         <v>1004</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>10</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>1005</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>10</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>103023</v>
       </c>
@@ -2186,23 +2304,26 @@
       <c r="F19" t="s">
         <v>78</v>
       </c>
-      <c r="I19">
+      <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="J19">
         <v>1004</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>100</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>1005</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>100</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>110001</v>
       </c>
@@ -2221,11 +2342,14 @@
       <c r="F20" t="s">
         <v>78</v>
       </c>
-      <c r="M20" t="s">
+      <c r="G20" t="s">
+        <v>86</v>
+      </c>
+      <c r="N20" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>110002</v>
       </c>
@@ -2244,11 +2368,14 @@
       <c r="F21" t="s">
         <v>78</v>
       </c>
-      <c r="M21" t="s">
+      <c r="G21" t="s">
+        <v>86</v>
+      </c>
+      <c r="N21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>110003</v>
       </c>
@@ -2267,11 +2394,14 @@
       <c r="F22" t="s">
         <v>78</v>
       </c>
-      <c r="M22" t="s">
+      <c r="G22" t="s">
+        <v>86</v>
+      </c>
+      <c r="N22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>110004</v>
       </c>
@@ -2290,11 +2420,14 @@
       <c r="F23" t="s">
         <v>78</v>
       </c>
-      <c r="M23" t="s">
+      <c r="G23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>110005</v>
       </c>
@@ -2313,11 +2446,14 @@
       <c r="F24" t="s">
         <v>78</v>
       </c>
-      <c r="M24" t="s">
+      <c r="G24" t="s">
+        <v>86</v>
+      </c>
+      <c r="N24" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>111001</v>
       </c>
@@ -2336,11 +2472,14 @@
       <c r="F25" t="s">
         <v>78</v>
       </c>
-      <c r="M25" t="s">
+      <c r="G25" t="s">
+        <v>87</v>
+      </c>
+      <c r="N25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>111002</v>
       </c>
@@ -2359,11 +2498,14 @@
       <c r="F26" t="s">
         <v>78</v>
       </c>
-      <c r="M26" t="s">
+      <c r="G26" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>111003</v>
       </c>
@@ -2382,11 +2524,14 @@
       <c r="F27" t="s">
         <v>78</v>
       </c>
-      <c r="M27" t="s">
+      <c r="G27" t="s">
+        <v>87</v>
+      </c>
+      <c r="N27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>111004</v>
       </c>
@@ -2405,11 +2550,14 @@
       <c r="F28" t="s">
         <v>78</v>
       </c>
-      <c r="M28" t="s">
+      <c r="G28" t="s">
+        <v>87</v>
+      </c>
+      <c r="N28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>111005</v>
       </c>
@@ -2428,11 +2576,14 @@
       <c r="F29" t="s">
         <v>78</v>
       </c>
-      <c r="M29" t="s">
+      <c r="G29" t="s">
+        <v>87</v>
+      </c>
+      <c r="N29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>112001</v>
       </c>
@@ -2451,7 +2602,10 @@
       <c r="F30" t="s">
         <v>82</v>
       </c>
-      <c r="M30" t="s">
+      <c r="G30" t="s">
+        <v>100</v>
+      </c>
+      <c r="N30" t="s">
         <v>84</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFCF54F-ECA3-4825-B688-9C439987BE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -195,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -575,13 +576,6 @@
     <t>laboratory5</t>
   </si>
   <si>
-    <t>ActionClassName</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>HelloFacilityAction</t>
-  </si>
-  <si>
     <t>drill1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -594,10 +588,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>DrillAction</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Coordinates</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -667,13 +657,25 @@
   </si>
   <si>
     <t>거대 드릴을 작동하기 위한 모터 시설이다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityClassName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FacilityEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DrillEntity</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1351,23 +1353,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:N30" totalsRowShown="0">
-  <autoFilter ref="A1:N30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:N30" totalsRowShown="0">
+  <autoFilter ref="A1:N30" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="5" name="Name"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="8" name="Type"/>
-    <tableColumn id="3" name="Level"/>
-    <tableColumn id="13" name="ActionClassName"/>
-    <tableColumn id="15" name="Desc"/>
-    <tableColumn id="11" name="BuildResourceId"/>
-    <tableColumn id="12" name="BuildResourceCount"/>
-    <tableColumn id="7" name="InputItemId"/>
-    <tableColumn id="10" name="InputItemCount"/>
-    <tableColumn id="6" name="OutputItemId"/>
-    <tableColumn id="9" name="OutputItemCount"/>
-    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="EntityClassName"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Desc"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1635,7 +1637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1666,10 +1668,10 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H1" t="s">
         <v>46</v>
@@ -1690,7 +1692,7 @@
         <v>22</v>
       </c>
       <c r="N1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -1710,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L2">
         <v>1001</v>
@@ -1742,10 +1744,10 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L3">
         <v>1001</v>
@@ -1774,10 +1776,10 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L4">
         <v>1001</v>
@@ -1806,10 +1808,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J5">
         <v>1001</v>
@@ -1844,10 +1846,10 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J6">
         <v>1001</v>
@@ -1882,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J7">
         <v>1001</v>
@@ -1920,10 +1922,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L8">
         <v>1003</v>
@@ -1952,10 +1954,10 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L9">
         <v>1003</v>
@@ -1984,10 +1986,10 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L10">
         <v>1003</v>
@@ -2016,10 +2018,10 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>1003</v>
@@ -2054,10 +2056,10 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J12">
         <v>1003</v>
@@ -2092,10 +2094,10 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J13">
         <v>1003</v>
@@ -2130,10 +2132,10 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L14">
         <v>1005</v>
@@ -2162,10 +2164,10 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L15">
         <v>1005</v>
@@ -2194,10 +2196,10 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L16">
         <v>1005</v>
@@ -2226,10 +2228,10 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J17">
         <v>1004</v>
@@ -2264,10 +2266,10 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J18">
         <v>1004</v>
@@ -2302,10 +2304,10 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J19">
         <v>1004</v>
@@ -2340,10 +2342,10 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N20" t="s">
         <v>49</v>
@@ -2366,10 +2368,10 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N21" t="s">
         <v>49</v>
@@ -2392,10 +2394,10 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N22" t="s">
         <v>49</v>
@@ -2418,10 +2420,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N23" t="s">
         <v>49</v>
@@ -2444,10 +2446,10 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N24" t="s">
         <v>49</v>
@@ -2470,10 +2472,10 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N25" t="s">
         <v>48</v>
@@ -2496,10 +2498,10 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N26" t="s">
         <v>48</v>
@@ -2522,10 +2524,10 @@
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N27" t="s">
         <v>48</v>
@@ -2548,10 +2550,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N28" t="s">
         <v>48</v>
@@ -2574,10 +2576,10 @@
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N29" t="s">
         <v>48</v>
@@ -2588,25 +2590,25 @@
         <v>112001</v>
       </c>
       <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" t="s">
         <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>81</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFCF54F-ECA3-4825-B688-9C439987BE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9CD7B4-EBF8-4CE4-9DED-9A348D4B4A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="104">
   <si>
     <t>0,0</t>
   </si>
@@ -669,6 +669,18 @@
   </si>
   <si>
     <t>DrillEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LabEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProcessEntity</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1712,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G2" t="s">
         <v>87</v>
@@ -1744,7 +1756,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
         <v>88</v>
@@ -1776,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s">
         <v>87</v>
@@ -1808,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
         <v>90</v>
@@ -1846,7 +1858,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
         <v>89</v>
@@ -1884,7 +1896,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -1922,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G8" t="s">
         <v>92</v>
@@ -1954,7 +1966,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G9" t="s">
         <v>93</v>
@@ -1986,7 +1998,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G10" t="s">
         <v>94</v>
@@ -2018,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
         <v>95</v>
@@ -2056,7 +2068,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
         <v>95</v>
@@ -2094,7 +2106,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
         <v>96</v>
@@ -2132,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G14" t="s">
         <v>85</v>
@@ -2164,7 +2176,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G15" t="s">
         <v>85</v>
@@ -2196,7 +2208,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G16" t="s">
         <v>85</v>
@@ -2228,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G17" t="s">
         <v>86</v>
@@ -2266,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G18" t="s">
         <v>86</v>
@@ -2304,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
         <v>86</v>
@@ -2342,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G20" t="s">
         <v>83</v>
@@ -2368,7 +2380,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
         <v>83</v>
@@ -2394,7 +2406,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
         <v>83</v>
@@ -2420,7 +2432,7 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G23" t="s">
         <v>83</v>
@@ -2446,7 +2458,7 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G24" t="s">
         <v>83</v>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9CD7B4-EBF8-4CE4-9DED-9A348D4B4A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -20,12 +19,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -303,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="118">
   <si>
     <t>0,0</t>
   </si>
@@ -681,13 +680,69 @@
   </si>
   <si>
     <t>ProcessEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>labIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>labIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>drillIcon</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -877,7 +932,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1057,8 +1112,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1173,6 +1234,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1302,8 +1376,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1365,23 +1445,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:N30" totalsRowShown="0">
-  <autoFilter ref="A1:N30" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="EntityClassName"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Desc"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:O30" totalsRowShown="0">
+  <autoFilter ref="A1:O30"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="5" name="Name"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="8" name="Type"/>
+    <tableColumn id="14" name="Icon"/>
+    <tableColumn id="3" name="Level"/>
+    <tableColumn id="13" name="EntityClassName"/>
+    <tableColumn id="15" name="Desc"/>
+    <tableColumn id="11" name="BuildResourceId"/>
+    <tableColumn id="12" name="BuildResourceCount"/>
+    <tableColumn id="7" name="InputItemId"/>
+    <tableColumn id="10" name="InputItemCount"/>
+    <tableColumn id="6" name="OutputItemId"/>
+    <tableColumn id="9" name="OutputItemCount"/>
+    <tableColumn id="4" name="Coordinates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1649,8 +1730,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.25" customWidth="1"/>
@@ -1663,7 +1744,7 @@
     <col min="13" max="13" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1677,37 +1758,40 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>98</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>82</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>46</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101011</v>
       </c>
@@ -1720,26 +1804,29 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>101</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>87</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1001</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>1</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>101012</v>
       </c>
@@ -1752,26 +1839,29 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>101</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>88</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1001</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>10</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>101013</v>
       </c>
@@ -1784,26 +1874,29 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>101</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>87</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1001</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>100</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>101021</v>
       </c>
@@ -1816,32 +1909,35 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>103</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>90</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1001</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1002</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>101022</v>
       </c>
@@ -1854,32 +1950,35 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>103</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>89</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>1001</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1002</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>10</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>101023</v>
       </c>
@@ -1892,32 +1991,35 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>103</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>91</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1001</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>100</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1002</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>100</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>102011</v>
       </c>
@@ -1930,26 +2032,29 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>101</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>92</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1003</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>1</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>102012</v>
       </c>
@@ -1962,26 +2067,29 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>101</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>93</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>1003</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>10</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>102013</v>
       </c>
@@ -1994,26 +2102,29 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10">
         <v>3</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>101</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>94</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>1003</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>100</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>102021</v>
       </c>
@@ -2026,32 +2137,35 @@
       <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>103</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>95</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1003</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1004</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>1</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>102022</v>
       </c>
@@ -2064,32 +2178,35 @@
       <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12">
         <v>2</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>103</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>95</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>1003</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>10</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>1004</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>10</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>102023</v>
       </c>
@@ -2102,32 +2219,35 @@
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13">
         <v>3</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>103</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>96</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>1003</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>100</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1004</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>100</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>103011</v>
       </c>
@@ -2140,26 +2260,29 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>101</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>85</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1005</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>1</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>103012</v>
       </c>
@@ -2172,26 +2295,29 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>101</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>85</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>1005</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>10</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>103013</v>
       </c>
@@ -2204,26 +2330,29 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16">
         <v>3</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>101</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>85</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>1005</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>100</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>103021</v>
       </c>
@@ -2236,32 +2365,35 @@
       <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17">
         <v>1</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>103</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>86</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1004</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>1006</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>1</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>103022</v>
       </c>
@@ -2274,32 +2406,35 @@
       <c r="D18" t="s">
         <v>14</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>103</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>86</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>1004</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>10</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>1005</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>10</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>103023</v>
       </c>
@@ -2312,32 +2447,35 @@
       <c r="D19" t="s">
         <v>14</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19">
         <v>3</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>103</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>86</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>1004</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>100</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>1005</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>100</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>110001</v>
       </c>
@@ -2350,20 +2488,23 @@
       <c r="D20" t="s">
         <v>71</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>102</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>83</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>110002</v>
       </c>
@@ -2376,20 +2517,23 @@
       <c r="D21" t="s">
         <v>71</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>102</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>83</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>110003</v>
       </c>
@@ -2402,20 +2546,23 @@
       <c r="D22" t="s">
         <v>71</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22">
         <v>3</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>102</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>83</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>110004</v>
       </c>
@@ -2428,20 +2575,23 @@
       <c r="D23" t="s">
         <v>71</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>102</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>83</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>110005</v>
       </c>
@@ -2454,20 +2604,23 @@
       <c r="D24" t="s">
         <v>71</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24">
         <v>5</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>102</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>83</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>111001</v>
       </c>
@@ -2480,20 +2633,23 @@
       <c r="D25" t="s">
         <v>70</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>99</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>84</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>111002</v>
       </c>
@@ -2506,20 +2662,23 @@
       <c r="D26" t="s">
         <v>70</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26">
         <v>2</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>99</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>84</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>111003</v>
       </c>
@@ -2532,20 +2691,23 @@
       <c r="D27" t="s">
         <v>70</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27">
         <v>3</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>99</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>84</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>111004</v>
       </c>
@@ -2558,20 +2720,23 @@
       <c r="D28" t="s">
         <v>70</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28">
         <v>4</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>99</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>84</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>111005</v>
       </c>
@@ -2584,20 +2749,23 @@
       <c r="D29" t="s">
         <v>70</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29">
         <v>5</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>99</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>84</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>112001</v>
       </c>
@@ -2610,16 +2778,19 @@
       <c r="D30" t="s">
         <v>79</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30">
         <v>1</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>100</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>97</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>81</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -195,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="206">
   <si>
     <t>0,0</t>
   </si>
@@ -363,24 +363,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>돌 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>돌 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>돌 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>돌 가공 시설 Lv.3</t>
-  </si>
-  <si>
     <t>InputItemCount</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -480,9 +462,6 @@
   </si>
   <si>
     <t>0,0;0,1;1,0;1,1</t>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0;1,1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -499,243 +478,576 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>stone_miner2</t>
-  </si>
-  <si>
-    <t>stone_miner3</t>
-  </si>
-  <si>
     <t>stone_processor1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>stone_processor2</t>
-  </si>
-  <si>
-    <t>stone_processor3</t>
+    <t>engine_merger1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger2</t>
+  </si>
+  <si>
+    <t>engine_merger3</t>
+  </si>
+  <si>
+    <t>engine_merger4</t>
+  </si>
+  <si>
+    <t>engine_merger5</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>EngineMerger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laboratory</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory2</t>
+  </si>
+  <si>
+    <t>laboratory3</t>
+  </si>
+  <si>
+    <t>laboratory4</t>
+  </si>
+  <si>
+    <t>laboratory5</t>
+  </si>
+  <si>
+    <t>Coordinates</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구를 진행하여 공장을 강화할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 엔진을 개발하거나, 기존의 엔진들을 합성할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 광석을 철 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityClassName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FacilityEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LabEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProcessEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>labIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>labIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireResearchId</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>gold_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>obsidian_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner2</t>
+  </si>
+  <si>
+    <t>obsidian_miner3</t>
+  </si>
+  <si>
+    <t>obsidian_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor2</t>
+  </si>
+  <si>
+    <t>obsidian_processor3</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>금 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner2</t>
+  </si>
+  <si>
+    <t>gold_miner3</t>
+  </si>
+  <si>
+    <t>gold_processor2</t>
+  </si>
+  <si>
+    <t>gold_processor3</t>
+  </si>
+  <si>
+    <t>tunstein_miner2</t>
+  </si>
+  <si>
+    <t>tunstein_miner3</t>
+  </si>
+  <si>
+    <t>tunstein_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_processor2</t>
+  </si>
+  <si>
+    <t>tunstein_processor3</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>텅스텐 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 광석을 텅스텐 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 광석을 흑요석 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 광석을 금 자재로 가공할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor2</t>
+  </si>
+  <si>
+    <t>titanium_processor3</t>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 광석을 생산할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>티타늄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 광석을 티타늄 자재로 가공할 수 있다.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 드릴</t>
+  </si>
+  <si>
+    <t>거대 구리 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>drill2</t>
+  </si>
+  <si>
+    <t>drill3</t>
+  </si>
+  <si>
+    <t>drill4</t>
+  </si>
+  <si>
+    <t>drill5</t>
+  </si>
+  <si>
+    <t>drill6</t>
+  </si>
+  <si>
+    <t>drill7</t>
+  </si>
+  <si>
+    <t>거대 돌 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 철 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 금 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 흑요석 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 텅스텐 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 티타늄 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>돌 드릴</t>
+  </si>
+  <si>
+    <t>철 드릴</t>
+  </si>
+  <si>
+    <t>금 드릴</t>
+  </si>
+  <si>
+    <t>흑요석 드릴</t>
+  </si>
+  <si>
+    <t>텅스텐 드릴</t>
+  </si>
+  <si>
+    <t>티타늄 드릴</t>
+  </si>
+  <si>
+    <t>engine_merger6</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>engine_merger7</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>drill1</t>
+  </si>
+  <si>
+    <t>Drill</t>
+  </si>
+  <si>
+    <t>drillIcon</t>
+  </si>
+  <si>
+    <t>DrillEntity</t>
+  </si>
+  <si>
+    <t>resource_merger1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceMerger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잉여 자원을 재활용하기 위한 시설이다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireCoreLevel</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory6</t>
+  </si>
+  <si>
+    <t>연구소 Lv.6</t>
+  </si>
+  <si>
+    <t>laboratory7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.7</t>
   </si>
   <si>
     <t>연구소 Lv.5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_merger1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_merger2</t>
-  </si>
-  <si>
-    <t>engine_merger3</t>
-  </si>
-  <si>
-    <t>engine_merger4</t>
-  </si>
-  <si>
-    <t>engine_merger5</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.2</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.3</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.4</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.5</t>
-  </si>
-  <si>
-    <t>EngineMerger</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Laboratory</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>laboratory1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>laboratory2</t>
-  </si>
-  <si>
-    <t>laboratory3</t>
-  </si>
-  <si>
-    <t>laboratory4</t>
-  </si>
-  <si>
-    <t>laboratory5</t>
-  </si>
-  <si>
-    <t>drill1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>드릴 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Drill</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coordinates</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구를 진행하여 공장을 강화할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>새로운 엔진을 개발하거나, 기존의 엔진들을 합성할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 광석을 철 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>거대 드릴을 작동하기 위한 모터 시설이다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EntityClassName</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FacilityEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DrillEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MinerEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LabEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProcessEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>labIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>labIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>drillIcon</t>
+  </si>
+  <si>
+    <t>resource_merger2</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>resource_merger3</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>resource_merger4</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>resource_merger5</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger6</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>resource_merger7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>0,0;0,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +1055,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -930,6 +1242,14 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1119,7 +1439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1247,6 +1567,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1376,7 +1731,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1384,6 +1739,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1445,9 +1824,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:O30" totalsRowShown="0">
-  <autoFilter ref="A1:O30"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:Q67" totalsRowShown="0">
+  <autoFilter ref="A1:Q67"/>
+  <tableColumns count="17">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="5" name="Name"/>
     <tableColumn id="2" name="DisplayName"/>
@@ -1456,6 +1835,8 @@
     <tableColumn id="3" name="Level"/>
     <tableColumn id="13" name="EntityClassName"/>
     <tableColumn id="15" name="Desc"/>
+    <tableColumn id="16" name="RequireResearchId"/>
+    <tableColumn id="18" name="RequireCoreLevel"/>
     <tableColumn id="11" name="BuildResourceId"/>
     <tableColumn id="12" name="BuildResourceCount"/>
     <tableColumn id="7" name="InputItemId"/>
@@ -1731,7 +2112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.25" customWidth="1"/>
@@ -1739,12 +2120,15 @@
     <col min="4" max="4" width="24.125" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="40.25" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="8" max="8" width="36.125" customWidth="1"/>
+    <col min="9" max="9" width="26.875" customWidth="1"/>
+    <col min="10" max="10" width="31.625" customWidth="1"/>
+    <col min="11" max="11" width="27" customWidth="1"/>
     <col min="12" max="12" width="18.125" customWidth="1"/>
     <col min="13" max="13" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1758,45 +2142,51 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="K1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101011</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -1805,993 +2195,2512 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M2">
+        <v>71</v>
+      </c>
+      <c r="O2">
         <v>1001</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>1</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>101012</v>
+        <v>101021</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="M3">
         <v>1001</v>
       </c>
       <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1002</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>102011</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4">
+        <v>30001</v>
+      </c>
+      <c r="O4">
+        <v>1003</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>102012</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5">
+        <v>30002</v>
+      </c>
+      <c r="O5">
+        <v>1003</v>
+      </c>
+      <c r="P5">
         <v>10</v>
       </c>
-      <c r="O3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>101013</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4">
+      <c r="Q5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>102013</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M4">
-        <v>1001</v>
-      </c>
-      <c r="N4">
+      <c r="G6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6">
+        <v>30003</v>
+      </c>
+      <c r="O6">
+        <v>1003</v>
+      </c>
+      <c r="P6">
         <v>100</v>
       </c>
-      <c r="O4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>101021</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" t="s">
-        <v>90</v>
-      </c>
-      <c r="K5">
-        <v>1001</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1002</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>101022</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="Q6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>102021</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K6">
-        <v>1001</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>1002</v>
-      </c>
-      <c r="N6">
-        <v>10</v>
-      </c>
-      <c r="O6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>101023</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K7">
-        <v>1001</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
+        <v>76</v>
+      </c>
+      <c r="I7">
+        <v>30001</v>
       </c>
       <c r="M7">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1004</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>102011</v>
+        <v>102022</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>76</v>
+      </c>
+      <c r="I8">
+        <v>30002</v>
       </c>
       <c r="M8">
         <v>1003</v>
       </c>
       <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>1004</v>
+      </c>
+      <c r="P8">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>102012</v>
+        <v>102023</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s">
-        <v>93</v>
+        <v>77</v>
+      </c>
+      <c r="I9">
+        <v>30003</v>
       </c>
       <c r="M9">
         <v>1003</v>
       </c>
       <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
+        <v>1004</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>103011</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
         <v>10</v>
       </c>
-      <c r="O9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>102013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10">
+        <v>30006</v>
+      </c>
+      <c r="O10">
+        <v>1005</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>103012</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11">
+        <v>30007</v>
+      </c>
+      <c r="O11">
+        <v>1005</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>103013</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12">
+        <v>30008</v>
+      </c>
+      <c r="O12">
+        <v>1005</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>103021</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
         <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" t="s">
-        <v>94</v>
-      </c>
-      <c r="M10">
-        <v>1003</v>
-      </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>102021</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K11">
-        <v>1003</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1004</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>102022</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" t="s">
-        <v>95</v>
-      </c>
-      <c r="K12">
-        <v>1003</v>
-      </c>
-      <c r="L12">
-        <v>10</v>
-      </c>
-      <c r="M12">
-        <v>1004</v>
-      </c>
-      <c r="N12">
-        <v>10</v>
-      </c>
-      <c r="O12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>102023</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13">
-        <v>1003</v>
-      </c>
-      <c r="L13">
-        <v>100</v>
+        <v>70</v>
+      </c>
+      <c r="I13">
+        <v>30006</v>
       </c>
       <c r="M13">
         <v>1004</v>
       </c>
       <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1006</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>103022</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14">
+        <v>30007</v>
+      </c>
+      <c r="M14">
+        <v>1004</v>
+      </c>
+      <c r="N14">
+        <v>10</v>
+      </c>
+      <c r="O14">
+        <v>1005</v>
+      </c>
+      <c r="P14">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>103023</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15">
+        <v>30008</v>
+      </c>
+      <c r="M15">
+        <v>1004</v>
+      </c>
+      <c r="N15">
         <v>100</v>
       </c>
-      <c r="O13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>103011</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="O15">
+        <v>1005</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>104011</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16">
+        <v>30011</v>
+      </c>
+      <c r="O16">
+        <v>1007</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>104012</v>
+      </c>
+      <c r="B17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17">
+        <v>30012</v>
+      </c>
+      <c r="O17">
+        <v>1007</v>
+      </c>
+      <c r="P17">
         <v>10</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="M14">
-        <v>1005</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>103012</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M15">
-        <v>1005</v>
-      </c>
-      <c r="N15">
-        <v>10</v>
-      </c>
-      <c r="O15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>103013</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16">
+      <c r="Q17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>104013</v>
+      </c>
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18">
         <v>3</v>
       </c>
-      <c r="G16" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" t="s">
-        <v>85</v>
-      </c>
-      <c r="M16">
-        <v>1005</v>
-      </c>
-      <c r="N16">
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18">
+        <v>30013</v>
+      </c>
+      <c r="O18">
+        <v>1007</v>
+      </c>
+      <c r="P18">
         <v>100</v>
       </c>
-      <c r="O16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>103021</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" t="s">
-        <v>86</v>
-      </c>
-      <c r="K17">
-        <v>1004</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1006</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>103022</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K18">
-        <v>1004</v>
-      </c>
-      <c r="L18">
-        <v>10</v>
-      </c>
-      <c r="M18">
-        <v>1005</v>
-      </c>
-      <c r="N18">
-        <v>10</v>
-      </c>
-      <c r="O18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>103023</v>
+        <v>104021</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I19">
+        <v>30011</v>
+      </c>
+      <c r="M19">
+        <v>1007</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1008</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>104022</v>
+      </c>
+      <c r="B20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" t="s">
+        <v>139</v>
+      </c>
+      <c r="I20">
+        <v>30012</v>
+      </c>
+      <c r="M20">
+        <v>1007</v>
+      </c>
+      <c r="N20">
+        <v>10</v>
+      </c>
+      <c r="O20">
+        <v>1008</v>
+      </c>
+      <c r="P20">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>104023</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" t="s">
+        <v>139</v>
+      </c>
+      <c r="I21">
+        <v>30013</v>
+      </c>
+      <c r="M21">
+        <v>1007</v>
+      </c>
+      <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>1008</v>
+      </c>
+      <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>105011</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22">
+        <v>30016</v>
+      </c>
+      <c r="O22">
+        <v>1009</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>105012</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
         <v>111</v>
       </c>
-      <c r="F19">
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23">
+        <v>30017</v>
+      </c>
+      <c r="O23">
+        <v>1009</v>
+      </c>
+      <c r="P23">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>105013</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24">
         <v>3</v>
       </c>
-      <c r="G19" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" t="s">
-        <v>86</v>
-      </c>
-      <c r="K19">
-        <v>1004</v>
-      </c>
-      <c r="L19">
+      <c r="G24" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24">
+        <v>30018</v>
+      </c>
+      <c r="O24">
+        <v>1009</v>
+      </c>
+      <c r="P24">
         <v>100</v>
       </c>
-      <c r="M19">
-        <v>1005</v>
-      </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>110001</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="Q24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>105021</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" t="s">
         <v>113</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H20" t="s">
-        <v>83</v>
-      </c>
-      <c r="O20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>110002</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>102</v>
-      </c>
-      <c r="H21" t="s">
-        <v>83</v>
-      </c>
-      <c r="O21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>110003</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22" t="s">
-        <v>102</v>
-      </c>
-      <c r="H22" t="s">
-        <v>83</v>
-      </c>
-      <c r="O22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>110004</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23">
-        <v>4</v>
-      </c>
-      <c r="G23" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" t="s">
-        <v>83</v>
-      </c>
-      <c r="O23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>110005</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-      <c r="G24" t="s">
-        <v>102</v>
-      </c>
-      <c r="H24" t="s">
-        <v>83</v>
-      </c>
-      <c r="O24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>111001</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25">
+        <v>30016</v>
+      </c>
+      <c r="M25">
+        <v>1009</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1010</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>105022</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="O25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>111002</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26">
+        <v>30017</v>
+      </c>
+      <c r="M26">
+        <v>1009</v>
+      </c>
+      <c r="N26">
+        <v>10</v>
+      </c>
+      <c r="O26">
+        <v>1010</v>
+      </c>
+      <c r="P26">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>105023</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="O26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>111003</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27">
+        <v>30018</v>
+      </c>
+      <c r="M27">
+        <v>1009</v>
+      </c>
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
+        <v>1010</v>
+      </c>
+      <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>106011</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="O27" t="s">
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28">
+        <v>30021</v>
+      </c>
+      <c r="O28">
+        <v>1011</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>106012</v>
+      </c>
+      <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29">
+        <v>30022</v>
+      </c>
+      <c r="O29">
+        <v>1011</v>
+      </c>
+      <c r="P29">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>106013</v>
+      </c>
+      <c r="B30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s">
+        <v>136</v>
+      </c>
+      <c r="I30">
+        <v>30023</v>
+      </c>
+      <c r="O30">
+        <v>1011</v>
+      </c>
+      <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>106021</v>
+      </c>
+      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s">
+        <v>137</v>
+      </c>
+      <c r="I31">
+        <v>30021</v>
+      </c>
+      <c r="M31">
+        <v>1011</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>1012</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>106022</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s">
+        <v>137</v>
+      </c>
+      <c r="I32">
+        <v>30022</v>
+      </c>
+      <c r="M32">
+        <v>1011</v>
+      </c>
+      <c r="N32">
+        <v>10</v>
+      </c>
+      <c r="O32">
+        <v>1012</v>
+      </c>
+      <c r="P32">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>106023</v>
+      </c>
+      <c r="B33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H33" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33">
+        <v>30023</v>
+      </c>
+      <c r="M33">
+        <v>1011</v>
+      </c>
+      <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="O33">
+        <v>1012</v>
+      </c>
+      <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>107011</v>
+      </c>
+      <c r="B34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34">
+        <v>30026</v>
+      </c>
+      <c r="O34">
+        <v>1013</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>107012</v>
+      </c>
+      <c r="B35" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s">
+        <v>152</v>
+      </c>
+      <c r="I35">
+        <v>30027</v>
+      </c>
+      <c r="O35">
+        <v>1013</v>
+      </c>
+      <c r="P35">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>107013</v>
+      </c>
+      <c r="B36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s">
+        <v>152</v>
+      </c>
+      <c r="I36">
+        <v>30028</v>
+      </c>
+      <c r="O36">
+        <v>1013</v>
+      </c>
+      <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>107021</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I37">
+        <v>30026</v>
+      </c>
+      <c r="M37">
+        <v>1013</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>1014</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>107022</v>
+      </c>
+      <c r="B38" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>82</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I38">
+        <v>30027</v>
+      </c>
+      <c r="M38">
+        <v>1013</v>
+      </c>
+      <c r="N38">
+        <v>10</v>
+      </c>
+      <c r="O38">
+        <v>1014</v>
+      </c>
+      <c r="P38">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>107023</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="7">
+        <v>3</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I39">
+        <v>30028</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39">
+        <v>1013</v>
+      </c>
+      <c r="N39" s="7">
+        <v>100</v>
+      </c>
+      <c r="O39">
+        <v>1014</v>
+      </c>
+      <c r="P39" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>110001</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
+        <v>110002</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="6">
+        <v>2</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6">
+        <v>2</v>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
+        <v>110003</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="6">
+        <v>3</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6">
+        <v>3</v>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
+        <v>110004</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="6">
+        <v>4</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6">
+        <v>4</v>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
+        <v>110005</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" s="6">
+        <v>5</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6">
+        <v>5</v>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
+        <v>110006</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="6">
+        <v>6</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6">
+        <v>6</v>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>110007</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" s="6">
+        <v>7</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6">
+        <v>7</v>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
+        <v>111001</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="C47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>111002</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="4">
+        <v>2</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="6">
+        <v>2</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
+        <v>111003</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="6">
+        <v>3</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6">
+        <v>3</v>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
         <v>111004</v>
       </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B50" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F50" s="4">
+        <v>4</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28">
+      <c r="I50" s="4"/>
+      <c r="J50" s="6">
         <v>4</v>
       </c>
-      <c r="G28" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" t="s">
-        <v>84</v>
-      </c>
-      <c r="O28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
         <v>111005</v>
       </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29">
+      <c r="B51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="6">
         <v>5</v>
       </c>
-      <c r="G29" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" t="s">
-        <v>84</v>
-      </c>
-      <c r="O29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="G51" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6">
+        <v>5</v>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
+        <v>111006</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" s="6">
+        <v>6</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6">
+        <v>6</v>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
+        <v>111007</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F53" s="6">
+        <v>7</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6">
+        <v>7</v>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6"/>
+      <c r="Q53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A54" s="10">
         <v>112001</v>
       </c>
-      <c r="B30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="B54" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F54" s="10">
+        <v>1</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>112002</v>
+      </c>
+      <c r="B55" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55" t="s">
+        <v>181</v>
+      </c>
+      <c r="H55" t="s">
+        <v>155</v>
+      </c>
+      <c r="I55">
+        <v>30005</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>112003</v>
+      </c>
+      <c r="B56" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" t="s">
+        <v>169</v>
+      </c>
+      <c r="D56" t="s">
+        <v>179</v>
+      </c>
+      <c r="E56" t="s">
+        <v>180</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56" t="s">
+        <v>181</v>
+      </c>
+      <c r="H56" t="s">
+        <v>163</v>
+      </c>
+      <c r="I56">
+        <v>30010</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>112004</v>
+      </c>
+      <c r="B57" t="s">
+        <v>158</v>
+      </c>
+      <c r="C57" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E57" t="s">
+        <v>180</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>181</v>
+      </c>
+      <c r="H57" t="s">
+        <v>164</v>
+      </c>
+      <c r="I57">
+        <v>30015</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>112005</v>
+      </c>
+      <c r="B58" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" t="s">
+        <v>171</v>
+      </c>
+      <c r="D58" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" t="s">
+        <v>180</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58" t="s">
+        <v>181</v>
+      </c>
+      <c r="H58" t="s">
+        <v>165</v>
+      </c>
+      <c r="I58">
+        <v>30020</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>112006</v>
+      </c>
+      <c r="B59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59" t="s">
+        <v>172</v>
+      </c>
+      <c r="D59" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" t="s">
+        <v>180</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>181</v>
+      </c>
+      <c r="H59" t="s">
+        <v>166</v>
+      </c>
+      <c r="I59">
+        <v>30025</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>112007</v>
+      </c>
+      <c r="B60" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60">
+        <v>7</v>
+      </c>
+      <c r="G60" t="s">
+        <v>181</v>
+      </c>
+      <c r="H60" t="s">
+        <v>167</v>
+      </c>
+      <c r="I60">
+        <v>30030</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>113001</v>
+      </c>
+      <c r="B61" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" t="s">
+        <v>184</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
         <v>79</v>
       </c>
-      <c r="E30" t="s">
-        <v>117</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" t="s">
-        <v>97</v>
-      </c>
-      <c r="O30" t="s">
-        <v>81</v>
+      <c r="H61" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>113002</v>
+      </c>
+      <c r="B62" t="s">
+        <v>192</v>
+      </c>
+      <c r="C62" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" t="s">
+        <v>184</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s">
+        <v>185</v>
+      </c>
+      <c r="J62" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>113003</v>
+      </c>
+      <c r="B63" t="s">
+        <v>194</v>
+      </c>
+      <c r="C63" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" t="s">
+        <v>184</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="G63" t="s">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J63" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>113004</v>
+      </c>
+      <c r="B64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" t="s">
+        <v>197</v>
+      </c>
+      <c r="D64" t="s">
+        <v>184</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64" t="s">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s">
+        <v>185</v>
+      </c>
+      <c r="J64" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>113005</v>
+      </c>
+      <c r="B65" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" t="s">
+        <v>199</v>
+      </c>
+      <c r="D65" t="s">
+        <v>184</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65" t="s">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s">
+        <v>185</v>
+      </c>
+      <c r="J65" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>113006</v>
+      </c>
+      <c r="B66" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" t="s">
+        <v>201</v>
+      </c>
+      <c r="D66" t="s">
+        <v>184</v>
+      </c>
+      <c r="F66">
+        <v>6</v>
+      </c>
+      <c r="G66" t="s">
+        <v>79</v>
+      </c>
+      <c r="H66" t="s">
+        <v>185</v>
+      </c>
+      <c r="J66" s="6">
+        <v>6</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>113007</v>
+      </c>
+      <c r="B67" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" t="s">
+        <v>203</v>
+      </c>
+      <c r="D67" t="s">
+        <v>184</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67" t="s">
+        <v>79</v>
+      </c>
+      <c r="H67" t="s">
+        <v>185</v>
+      </c>
+      <c r="J67" s="6">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="207">
   <si>
     <t>0,0</t>
   </si>
@@ -1048,6 +1048,10 @@
   </si>
   <si>
     <t>0,0;0,1;0,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>resourceMergerIcon</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -4519,6 +4523,9 @@
       <c r="D61" t="s">
         <v>184</v>
       </c>
+      <c r="E61" t="s">
+        <v>206</v>
+      </c>
       <c r="F61">
         <v>1</v>
       </c>
@@ -4545,6 +4552,9 @@
       <c r="D62" t="s">
         <v>184</v>
       </c>
+      <c r="E62" t="s">
+        <v>206</v>
+      </c>
       <c r="F62">
         <v>2</v>
       </c>
@@ -4574,6 +4584,9 @@
       <c r="D63" t="s">
         <v>184</v>
       </c>
+      <c r="E63" t="s">
+        <v>206</v>
+      </c>
       <c r="F63">
         <v>3</v>
       </c>
@@ -4603,6 +4616,9 @@
       <c r="D64" t="s">
         <v>184</v>
       </c>
+      <c r="E64" t="s">
+        <v>206</v>
+      </c>
       <c r="F64">
         <v>4</v>
       </c>
@@ -4632,6 +4648,9 @@
       <c r="D65" t="s">
         <v>184</v>
       </c>
+      <c r="E65" t="s">
+        <v>206</v>
+      </c>
       <c r="F65">
         <v>5</v>
       </c>
@@ -4661,6 +4680,9 @@
       <c r="D66" t="s">
         <v>184</v>
       </c>
+      <c r="E66" t="s">
+        <v>206</v>
+      </c>
       <c r="F66">
         <v>6</v>
       </c>
@@ -4689,6 +4711,9 @@
       </c>
       <c r="D67" t="s">
         <v>184</v>
+      </c>
+      <c r="E67" t="s">
+        <v>206</v>
       </c>
       <c r="F67">
         <v>7</v>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -2210,6 +2210,12 @@
       <c r="H2" t="s">
         <v>71</v>
       </c>
+      <c r="K2">
+        <v>1002</v>
+      </c>
+      <c r="L2" s="10">
+        <v>10000</v>
+      </c>
       <c r="O2">
         <v>1001</v>
       </c>
@@ -2245,6 +2251,12 @@
       <c r="H3" t="s">
         <v>72</v>
       </c>
+      <c r="K3">
+        <v>1002</v>
+      </c>
+      <c r="L3" s="10">
+        <v>10000</v>
+      </c>
       <c r="M3">
         <v>1001</v>
       </c>
@@ -2289,6 +2301,12 @@
       <c r="I4">
         <v>30001</v>
       </c>
+      <c r="K4">
+        <v>1002</v>
+      </c>
+      <c r="L4" s="10">
+        <v>200</v>
+      </c>
       <c r="O4">
         <v>1003</v>
       </c>
@@ -2327,6 +2345,12 @@
       <c r="I5">
         <v>30002</v>
       </c>
+      <c r="K5">
+        <v>1004</v>
+      </c>
+      <c r="L5" s="10">
+        <v>2000</v>
+      </c>
       <c r="O5">
         <v>1003</v>
       </c>
@@ -2365,6 +2389,12 @@
       <c r="I6">
         <v>30003</v>
       </c>
+      <c r="K6">
+        <v>1004</v>
+      </c>
+      <c r="L6" s="10">
+        <v>30000</v>
+      </c>
       <c r="O6">
         <v>1003</v>
       </c>
@@ -2403,6 +2433,12 @@
       <c r="I7">
         <v>30001</v>
       </c>
+      <c r="K7">
+        <v>1002</v>
+      </c>
+      <c r="L7" s="10">
+        <v>200</v>
+      </c>
       <c r="M7">
         <v>1003</v>
       </c>
@@ -2447,6 +2483,12 @@
       <c r="I8">
         <v>30002</v>
       </c>
+      <c r="K8">
+        <v>1004</v>
+      </c>
+      <c r="L8" s="10">
+        <v>2000</v>
+      </c>
       <c r="M8">
         <v>1003</v>
       </c>
@@ -2491,6 +2533,12 @@
       <c r="I9">
         <v>30003</v>
       </c>
+      <c r="K9">
+        <v>1004</v>
+      </c>
+      <c r="L9" s="10">
+        <v>30000</v>
+      </c>
       <c r="M9">
         <v>1003</v>
       </c>
@@ -2535,6 +2583,12 @@
       <c r="I10">
         <v>30006</v>
       </c>
+      <c r="K10">
+        <v>1004</v>
+      </c>
+      <c r="L10" s="10">
+        <v>40000</v>
+      </c>
       <c r="O10">
         <v>1005</v>
       </c>
@@ -2573,6 +2627,12 @@
       <c r="I11">
         <v>30007</v>
       </c>
+      <c r="K11">
+        <v>1006</v>
+      </c>
+      <c r="L11" s="10">
+        <v>2000</v>
+      </c>
       <c r="O11">
         <v>1005</v>
       </c>
@@ -2611,6 +2671,12 @@
       <c r="I12">
         <v>30008</v>
       </c>
+      <c r="K12">
+        <v>1006</v>
+      </c>
+      <c r="L12" s="10">
+        <v>30000</v>
+      </c>
       <c r="O12">
         <v>1005</v>
       </c>
@@ -2649,6 +2715,12 @@
       <c r="I13">
         <v>30006</v>
       </c>
+      <c r="K13">
+        <v>1004</v>
+      </c>
+      <c r="L13" s="10">
+        <v>40000</v>
+      </c>
       <c r="M13">
         <v>1004</v>
       </c>
@@ -2693,6 +2765,12 @@
       <c r="I14">
         <v>30007</v>
       </c>
+      <c r="K14">
+        <v>1006</v>
+      </c>
+      <c r="L14" s="10">
+        <v>2000</v>
+      </c>
       <c r="M14">
         <v>1004</v>
       </c>
@@ -2737,6 +2815,12 @@
       <c r="I15">
         <v>30008</v>
       </c>
+      <c r="K15">
+        <v>1006</v>
+      </c>
+      <c r="L15" s="10">
+        <v>30000</v>
+      </c>
       <c r="M15">
         <v>1004</v>
       </c>
@@ -2781,6 +2865,12 @@
       <c r="I16">
         <v>30011</v>
       </c>
+      <c r="K16">
+        <v>1006</v>
+      </c>
+      <c r="L16" s="10">
+        <v>40000</v>
+      </c>
       <c r="O16">
         <v>1007</v>
       </c>
@@ -2819,6 +2909,12 @@
       <c r="I17">
         <v>30012</v>
       </c>
+      <c r="K17">
+        <v>1008</v>
+      </c>
+      <c r="L17" s="10">
+        <v>2000</v>
+      </c>
       <c r="O17">
         <v>1007</v>
       </c>
@@ -2857,6 +2953,12 @@
       <c r="I18">
         <v>30013</v>
       </c>
+      <c r="K18">
+        <v>1008</v>
+      </c>
+      <c r="L18" s="10">
+        <v>30000</v>
+      </c>
       <c r="O18">
         <v>1007</v>
       </c>
@@ -2895,6 +2997,12 @@
       <c r="I19">
         <v>30011</v>
       </c>
+      <c r="K19">
+        <v>1006</v>
+      </c>
+      <c r="L19" s="10">
+        <v>40000</v>
+      </c>
       <c r="M19">
         <v>1007</v>
       </c>
@@ -2939,6 +3047,12 @@
       <c r="I20">
         <v>30012</v>
       </c>
+      <c r="K20">
+        <v>1008</v>
+      </c>
+      <c r="L20" s="10">
+        <v>2000</v>
+      </c>
       <c r="M20">
         <v>1007</v>
       </c>
@@ -2983,6 +3097,12 @@
       <c r="I21">
         <v>30013</v>
       </c>
+      <c r="K21">
+        <v>1008</v>
+      </c>
+      <c r="L21" s="10">
+        <v>30000</v>
+      </c>
       <c r="M21">
         <v>1007</v>
       </c>
@@ -3027,6 +3147,12 @@
       <c r="I22">
         <v>30016</v>
       </c>
+      <c r="K22">
+        <v>1008</v>
+      </c>
+      <c r="L22" s="10">
+        <v>40000</v>
+      </c>
       <c r="O22">
         <v>1009</v>
       </c>
@@ -3065,6 +3191,12 @@
       <c r="I23">
         <v>30017</v>
       </c>
+      <c r="K23">
+        <v>1010</v>
+      </c>
+      <c r="L23" s="10">
+        <v>2000</v>
+      </c>
       <c r="O23">
         <v>1009</v>
       </c>
@@ -3103,6 +3235,12 @@
       <c r="I24">
         <v>30018</v>
       </c>
+      <c r="K24">
+        <v>1010</v>
+      </c>
+      <c r="L24" s="10">
+        <v>30000</v>
+      </c>
       <c r="O24">
         <v>1009</v>
       </c>
@@ -3141,6 +3279,12 @@
       <c r="I25">
         <v>30016</v>
       </c>
+      <c r="K25">
+        <v>1008</v>
+      </c>
+      <c r="L25" s="10">
+        <v>40000</v>
+      </c>
       <c r="M25">
         <v>1009</v>
       </c>
@@ -3185,6 +3329,12 @@
       <c r="I26">
         <v>30017</v>
       </c>
+      <c r="K26">
+        <v>1010</v>
+      </c>
+      <c r="L26" s="10">
+        <v>2000</v>
+      </c>
       <c r="M26">
         <v>1009</v>
       </c>
@@ -3229,6 +3379,12 @@
       <c r="I27">
         <v>30018</v>
       </c>
+      <c r="K27">
+        <v>1010</v>
+      </c>
+      <c r="L27" s="10">
+        <v>30000</v>
+      </c>
       <c r="M27">
         <v>1009</v>
       </c>
@@ -3273,6 +3429,12 @@
       <c r="I28">
         <v>30021</v>
       </c>
+      <c r="K28">
+        <v>1010</v>
+      </c>
+      <c r="L28" s="10">
+        <v>40000</v>
+      </c>
       <c r="O28">
         <v>1011</v>
       </c>
@@ -3311,6 +3473,12 @@
       <c r="I29">
         <v>30022</v>
       </c>
+      <c r="K29">
+        <v>1012</v>
+      </c>
+      <c r="L29" s="10">
+        <v>2000</v>
+      </c>
       <c r="O29">
         <v>1011</v>
       </c>
@@ -3349,6 +3517,12 @@
       <c r="I30">
         <v>30023</v>
       </c>
+      <c r="K30">
+        <v>1012</v>
+      </c>
+      <c r="L30" s="10">
+        <v>30000</v>
+      </c>
       <c r="O30">
         <v>1011</v>
       </c>
@@ -3387,6 +3561,12 @@
       <c r="I31">
         <v>30021</v>
       </c>
+      <c r="K31">
+        <v>1010</v>
+      </c>
+      <c r="L31" s="10">
+        <v>40000</v>
+      </c>
       <c r="M31">
         <v>1011</v>
       </c>
@@ -3431,6 +3611,12 @@
       <c r="I32">
         <v>30022</v>
       </c>
+      <c r="K32">
+        <v>1012</v>
+      </c>
+      <c r="L32" s="10">
+        <v>2000</v>
+      </c>
       <c r="M32">
         <v>1011</v>
       </c>
@@ -3475,6 +3661,12 @@
       <c r="I33">
         <v>30023</v>
       </c>
+      <c r="K33">
+        <v>1012</v>
+      </c>
+      <c r="L33" s="10">
+        <v>30000</v>
+      </c>
       <c r="M33">
         <v>1011</v>
       </c>
@@ -3519,6 +3711,12 @@
       <c r="I34">
         <v>30026</v>
       </c>
+      <c r="K34">
+        <v>1012</v>
+      </c>
+      <c r="L34" s="10">
+        <v>40000</v>
+      </c>
       <c r="O34">
         <v>1013</v>
       </c>
@@ -3557,6 +3755,12 @@
       <c r="I35">
         <v>30027</v>
       </c>
+      <c r="K35">
+        <v>1012</v>
+      </c>
+      <c r="L35" s="10">
+        <v>2000</v>
+      </c>
       <c r="O35">
         <v>1013</v>
       </c>
@@ -3595,6 +3799,12 @@
       <c r="I36">
         <v>30028</v>
       </c>
+      <c r="K36">
+        <v>1012</v>
+      </c>
+      <c r="L36" s="10">
+        <v>30000</v>
+      </c>
       <c r="O36">
         <v>1013</v>
       </c>
@@ -3633,6 +3843,12 @@
       <c r="I37">
         <v>30026</v>
       </c>
+      <c r="K37">
+        <v>1012</v>
+      </c>
+      <c r="L37" s="10">
+        <v>40000</v>
+      </c>
       <c r="M37">
         <v>1013</v>
       </c>
@@ -3677,6 +3893,12 @@
       <c r="I38">
         <v>30027</v>
       </c>
+      <c r="K38">
+        <v>1012</v>
+      </c>
+      <c r="L38" s="10">
+        <v>2000</v>
+      </c>
       <c r="M38">
         <v>1013</v>
       </c>
@@ -3721,8 +3943,12 @@
       <c r="I39">
         <v>30028</v>
       </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
+      <c r="K39">
+        <v>1012</v>
+      </c>
+      <c r="L39" s="10">
+        <v>30000</v>
+      </c>
       <c r="M39">
         <v>1013</v>
       </c>
@@ -3766,8 +3992,12 @@
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
+      <c r="K40" s="4">
+        <v>1002</v>
+      </c>
+      <c r="L40" s="10">
+        <v>5000</v>
+      </c>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
@@ -3805,8 +4035,12 @@
       <c r="J41" s="6">
         <v>2</v>
       </c>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
+      <c r="K41" s="6">
+        <v>1004</v>
+      </c>
+      <c r="L41" s="10">
+        <v>20000</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
@@ -3844,8 +4078,12 @@
       <c r="J42" s="6">
         <v>3</v>
       </c>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
+      <c r="K42" s="4">
+        <v>1006</v>
+      </c>
+      <c r="L42" s="10">
+        <v>20000</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
@@ -3883,8 +4121,12 @@
       <c r="J43" s="6">
         <v>4</v>
       </c>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+      <c r="K43" s="6">
+        <v>1008</v>
+      </c>
+      <c r="L43" s="10">
+        <v>20000</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
@@ -3922,8 +4164,12 @@
       <c r="J44" s="6">
         <v>5</v>
       </c>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
+      <c r="K44" s="4">
+        <v>1010</v>
+      </c>
+      <c r="L44" s="10">
+        <v>20000</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
@@ -3961,8 +4207,12 @@
       <c r="J45" s="6">
         <v>6</v>
       </c>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
+      <c r="K45" s="6">
+        <v>1012</v>
+      </c>
+      <c r="L45" s="10">
+        <v>20000</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
@@ -4000,8 +4250,12 @@
       <c r="J46" s="6">
         <v>7</v>
       </c>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
+      <c r="K46" s="4">
+        <v>1014</v>
+      </c>
+      <c r="L46" s="10">
+        <v>20000</v>
+      </c>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
@@ -4037,8 +4291,12 @@
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
+      <c r="K47" s="6">
+        <v>1002</v>
+      </c>
+      <c r="L47" s="10">
+        <v>5000</v>
+      </c>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
       <c r="O47" s="6"/>
@@ -4076,8 +4334,12 @@
       <c r="J48" s="6">
         <v>2</v>
       </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
+      <c r="K48" s="4">
+        <v>1004</v>
+      </c>
+      <c r="L48" s="10">
+        <v>20000</v>
+      </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
@@ -4115,8 +4377,12 @@
       <c r="J49" s="6">
         <v>3</v>
       </c>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
+      <c r="K49" s="6">
+        <v>1006</v>
+      </c>
+      <c r="L49" s="10">
+        <v>20000</v>
+      </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
@@ -4154,8 +4420,12 @@
       <c r="J50" s="6">
         <v>4</v>
       </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
+      <c r="K50" s="4">
+        <v>1008</v>
+      </c>
+      <c r="L50" s="10">
+        <v>20000</v>
+      </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
@@ -4193,8 +4463,12 @@
       <c r="J51" s="6">
         <v>5</v>
       </c>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
+      <c r="K51" s="6">
+        <v>1010</v>
+      </c>
+      <c r="L51" s="10">
+        <v>20000</v>
+      </c>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -4232,8 +4506,12 @@
       <c r="J52" s="6">
         <v>6</v>
       </c>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="K52" s="6">
+        <v>1012</v>
+      </c>
+      <c r="L52" s="10">
+        <v>20000</v>
+      </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
@@ -4271,8 +4549,12 @@
       <c r="J53" s="6">
         <v>7</v>
       </c>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="K53" s="6">
+        <v>1014</v>
+      </c>
+      <c r="L53" s="10">
+        <v>20000</v>
+      </c>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
@@ -4535,6 +4817,12 @@
       <c r="H61" t="s">
         <v>185</v>
       </c>
+      <c r="K61">
+        <v>1002</v>
+      </c>
+      <c r="L61" s="10">
+        <v>5000</v>
+      </c>
       <c r="Q61" t="s">
         <v>204</v>
       </c>
@@ -4567,6 +4855,12 @@
       <c r="J62" s="6">
         <v>2</v>
       </c>
+      <c r="K62">
+        <v>1004</v>
+      </c>
+      <c r="L62" s="10">
+        <v>20000</v>
+      </c>
       <c r="Q62" t="s">
         <v>204</v>
       </c>
@@ -4599,6 +4893,12 @@
       <c r="J63" s="6">
         <v>3</v>
       </c>
+      <c r="K63">
+        <v>1006</v>
+      </c>
+      <c r="L63" s="10">
+        <v>20000</v>
+      </c>
       <c r="Q63" t="s">
         <v>204</v>
       </c>
@@ -4631,6 +4931,12 @@
       <c r="J64" s="6">
         <v>4</v>
       </c>
+      <c r="K64">
+        <v>1008</v>
+      </c>
+      <c r="L64" s="10">
+        <v>20000</v>
+      </c>
       <c r="Q64" t="s">
         <v>204</v>
       </c>
@@ -4663,6 +4969,12 @@
       <c r="J65" s="6">
         <v>5</v>
       </c>
+      <c r="K65">
+        <v>1010</v>
+      </c>
+      <c r="L65" s="10">
+        <v>20000</v>
+      </c>
       <c r="Q65" t="s">
         <v>204</v>
       </c>
@@ -4695,6 +5007,12 @@
       <c r="J66" s="6">
         <v>6</v>
       </c>
+      <c r="K66">
+        <v>1012</v>
+      </c>
+      <c r="L66" s="10">
+        <v>20000</v>
+      </c>
       <c r="Q66" t="s">
         <v>204</v>
       </c>
@@ -4726,6 +5044,12 @@
       </c>
       <c r="J67" s="6">
         <v>7</v>
+      </c>
+      <c r="K67">
+        <v>1014</v>
+      </c>
+      <c r="L67" s="10">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1C4167-45DF-4D95-BC75-E4E23D49C7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -195,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -302,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="208">
   <si>
     <t>0,0</t>
   </si>
@@ -591,10 +592,6 @@
   </si>
   <si>
     <t>EntityClassName</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FacilityEntity</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1054,11 +1051,19 @@
     <t>resourceMergerIcon</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>ResourceMergerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EngineMergerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1735,38 +1740,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1828,26 +1827,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:Q67" totalsRowShown="0">
-  <autoFilter ref="A1:Q67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:Q67" totalsRowShown="0">
+  <autoFilter ref="A1:Q67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="17">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="5" name="Name"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="8" name="Type"/>
-    <tableColumn id="14" name="Icon"/>
-    <tableColumn id="3" name="Level"/>
-    <tableColumn id="13" name="EntityClassName"/>
-    <tableColumn id="15" name="Desc"/>
-    <tableColumn id="16" name="RequireResearchId"/>
-    <tableColumn id="18" name="RequireCoreLevel"/>
-    <tableColumn id="11" name="BuildResourceId"/>
-    <tableColumn id="12" name="BuildResourceCount"/>
-    <tableColumn id="7" name="InputItemId"/>
-    <tableColumn id="10" name="InputItemCount"/>
-    <tableColumn id="6" name="OutputItemId"/>
-    <tableColumn id="9" name="OutputItemCount"/>
-    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Icon"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="EntityClassName"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Desc"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="RequireResearchId"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="RequireCoreLevel"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2115,7 +2114,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2146,7 +2145,7 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -2158,10 +2157,10 @@
         <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K1" t="s">
         <v>40</v>
@@ -2199,13 +2198,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
         <v>71</v>
@@ -2213,7 +2212,7 @@
       <c r="K2">
         <v>1002</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2">
         <v>10000</v>
       </c>
       <c r="O2">
@@ -2240,13 +2239,13 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s">
         <v>72</v>
@@ -2254,7 +2253,7 @@
       <c r="K3">
         <v>1002</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3">
         <v>10000</v>
       </c>
       <c r="M3">
@@ -2287,13 +2286,13 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
         <v>73</v>
@@ -2304,7 +2303,7 @@
       <c r="K4">
         <v>1002</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4">
         <v>200</v>
       </c>
       <c r="O4">
@@ -2331,13 +2330,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
         <v>74</v>
@@ -2348,7 +2347,7 @@
       <c r="K5">
         <v>1004</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5">
         <v>2000</v>
       </c>
       <c r="O5">
@@ -2358,7 +2357,7 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -2375,13 +2374,13 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s">
         <v>75</v>
@@ -2392,7 +2391,7 @@
       <c r="K6">
         <v>1004</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6">
         <v>30000</v>
       </c>
       <c r="O6">
@@ -2402,7 +2401,7 @@
         <v>100</v>
       </c>
       <c r="Q6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -2419,13 +2418,13 @@
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
         <v>76</v>
@@ -2436,7 +2435,7 @@
       <c r="K7">
         <v>1002</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7">
         <v>200</v>
       </c>
       <c r="M7">
@@ -2469,13 +2468,13 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s">
         <v>76</v>
@@ -2486,7 +2485,7 @@
       <c r="K8">
         <v>1004</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8">
         <v>2000</v>
       </c>
       <c r="M8">
@@ -2502,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -2519,13 +2518,13 @@
         <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
         <v>77</v>
@@ -2536,7 +2535,7 @@
       <c r="K9">
         <v>1004</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9">
         <v>30000</v>
       </c>
       <c r="M9">
@@ -2552,7 +2551,7 @@
         <v>100</v>
       </c>
       <c r="Q9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -2569,13 +2568,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
         <v>69</v>
@@ -2586,7 +2585,7 @@
       <c r="K10">
         <v>1004</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10">
         <v>40000</v>
       </c>
       <c r="O10">
@@ -2613,13 +2612,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
         <v>69</v>
@@ -2630,7 +2629,7 @@
       <c r="K11">
         <v>1006</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11">
         <v>2000</v>
       </c>
       <c r="O11">
@@ -2640,7 +2639,7 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -2657,13 +2656,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
         <v>69</v>
@@ -2674,7 +2673,7 @@
       <c r="K12">
         <v>1006</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12">
         <v>30000</v>
       </c>
       <c r="O12">
@@ -2684,7 +2683,7 @@
         <v>100</v>
       </c>
       <c r="Q12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -2701,13 +2700,13 @@
         <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
@@ -2718,7 +2717,7 @@
       <c r="K13">
         <v>1004</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13">
         <v>40000</v>
       </c>
       <c r="M13">
@@ -2751,13 +2750,13 @@
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
         <v>70</v>
@@ -2768,7 +2767,7 @@
       <c r="K14">
         <v>1006</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14">
         <v>2000</v>
       </c>
       <c r="M14">
@@ -2784,7 +2783,7 @@
         <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -2801,13 +2800,13 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
         <v>70</v>
@@ -2818,7 +2817,7 @@
       <c r="K15">
         <v>1006</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15">
         <v>30000</v>
       </c>
       <c r="M15">
@@ -2834,7 +2833,7 @@
         <v>100</v>
       </c>
       <c r="Q15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -2842,25 +2841,25 @@
         <v>104011</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I16">
         <v>30011</v>
@@ -2868,7 +2867,7 @@
       <c r="K16">
         <v>1006</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16">
         <v>40000</v>
       </c>
       <c r="O16">
@@ -2886,25 +2885,25 @@
         <v>104012</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I17">
         <v>30012</v>
@@ -2912,7 +2911,7 @@
       <c r="K17">
         <v>1008</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17">
         <v>2000</v>
       </c>
       <c r="O17">
@@ -2922,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -2930,25 +2929,25 @@
         <v>104013</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I18">
         <v>30013</v>
@@ -2956,7 +2955,7 @@
       <c r="K18">
         <v>1008</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18">
         <v>30000</v>
       </c>
       <c r="O18">
@@ -2966,7 +2965,7 @@
         <v>100</v>
       </c>
       <c r="Q18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -2974,25 +2973,25 @@
         <v>104021</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I19">
         <v>30011</v>
@@ -3000,7 +2999,7 @@
       <c r="K19">
         <v>1006</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19">
         <v>40000</v>
       </c>
       <c r="M19">
@@ -3024,25 +3023,25 @@
         <v>104022</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I20">
         <v>30012</v>
@@ -3050,7 +3049,7 @@
       <c r="K20">
         <v>1008</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20">
         <v>2000</v>
       </c>
       <c r="M20">
@@ -3066,7 +3065,7 @@
         <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -3074,25 +3073,25 @@
         <v>104023</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21">
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I21">
         <v>30013</v>
@@ -3100,7 +3099,7 @@
       <c r="K21">
         <v>1008</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21">
         <v>30000</v>
       </c>
       <c r="M21">
@@ -3116,7 +3115,7 @@
         <v>100</v>
       </c>
       <c r="Q21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -3124,25 +3123,25 @@
         <v>105011</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I22">
         <v>30016</v>
@@ -3150,7 +3149,7 @@
       <c r="K22">
         <v>1008</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22">
         <v>40000</v>
       </c>
       <c r="O22">
@@ -3168,25 +3167,25 @@
         <v>105012</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I23">
         <v>30017</v>
@@ -3194,7 +3193,7 @@
       <c r="K23">
         <v>1010</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23">
         <v>2000</v>
       </c>
       <c r="O23">
@@ -3204,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -3212,25 +3211,25 @@
         <v>105013</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I24">
         <v>30018</v>
@@ -3238,7 +3237,7 @@
       <c r="K24">
         <v>1010</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24">
         <v>30000</v>
       </c>
       <c r="O24">
@@ -3248,7 +3247,7 @@
         <v>100</v>
       </c>
       <c r="Q24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -3256,25 +3255,25 @@
         <v>105021</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I25">
         <v>30016</v>
@@ -3282,7 +3281,7 @@
       <c r="K25">
         <v>1008</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25">
         <v>40000</v>
       </c>
       <c r="M25">
@@ -3306,25 +3305,25 @@
         <v>105022</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I26">
         <v>30017</v>
@@ -3332,7 +3331,7 @@
       <c r="K26">
         <v>1010</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26">
         <v>2000</v>
       </c>
       <c r="M26">
@@ -3348,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -3356,25 +3355,25 @@
         <v>105023</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I27">
         <v>30018</v>
@@ -3382,7 +3381,7 @@
       <c r="K27">
         <v>1010</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27">
         <v>30000</v>
       </c>
       <c r="M27">
@@ -3398,7 +3397,7 @@
         <v>100</v>
       </c>
       <c r="Q27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -3406,25 +3405,25 @@
         <v>106011</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I28">
         <v>30021</v>
@@ -3432,7 +3431,7 @@
       <c r="K28">
         <v>1010</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28">
         <v>40000</v>
       </c>
       <c r="O28">
@@ -3450,25 +3449,25 @@
         <v>106012</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I29">
         <v>30022</v>
@@ -3476,7 +3475,7 @@
       <c r="K29">
         <v>1012</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29">
         <v>2000</v>
       </c>
       <c r="O29">
@@ -3486,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -3494,25 +3493,25 @@
         <v>106013</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F30">
         <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I30">
         <v>30023</v>
@@ -3520,7 +3519,7 @@
       <c r="K30">
         <v>1012</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30">
         <v>30000</v>
       </c>
       <c r="O30">
@@ -3530,7 +3529,7 @@
         <v>100</v>
       </c>
       <c r="Q30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -3538,25 +3537,25 @@
         <v>106021</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I31">
         <v>30021</v>
@@ -3564,7 +3563,7 @@
       <c r="K31">
         <v>1010</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31">
         <v>40000</v>
       </c>
       <c r="M31">
@@ -3588,25 +3587,25 @@
         <v>106022</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I32">
         <v>30022</v>
@@ -3614,7 +3613,7 @@
       <c r="K32">
         <v>1012</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32">
         <v>2000</v>
       </c>
       <c r="M32">
@@ -3630,7 +3629,7 @@
         <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
@@ -3638,25 +3637,25 @@
         <v>106023</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I33">
         <v>30023</v>
@@ -3664,7 +3663,7 @@
       <c r="K33">
         <v>1012</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33">
         <v>30000</v>
       </c>
       <c r="M33">
@@ -3680,7 +3679,7 @@
         <v>100</v>
       </c>
       <c r="Q33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -3688,25 +3687,25 @@
         <v>107011</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I34">
         <v>30026</v>
@@ -3714,7 +3713,7 @@
       <c r="K34">
         <v>1012</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34">
         <v>40000</v>
       </c>
       <c r="O34">
@@ -3732,25 +3731,25 @@
         <v>107012</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I35">
         <v>30027</v>
@@ -3758,7 +3757,7 @@
       <c r="K35">
         <v>1012</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35">
         <v>2000</v>
       </c>
       <c r="O35">
@@ -3768,7 +3767,7 @@
         <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
@@ -3776,25 +3775,25 @@
         <v>107013</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F36">
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I36">
         <v>30028</v>
@@ -3802,7 +3801,7 @@
       <c r="K36">
         <v>1012</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36">
         <v>30000</v>
       </c>
       <c r="O36">
@@ -3812,7 +3811,7 @@
         <v>100</v>
       </c>
       <c r="Q36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
@@ -3820,25 +3819,25 @@
         <v>107021</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>82</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>153</v>
+        <v>81</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="I37">
         <v>30026</v>
@@ -3846,7 +3845,7 @@
       <c r="K37">
         <v>1012</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37">
         <v>40000</v>
       </c>
       <c r="M37">
@@ -3870,25 +3869,25 @@
         <v>107022</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>82</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>153</v>
+        <v>81</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="I38">
         <v>30027</v>
@@ -3896,7 +3895,7 @@
       <c r="K38">
         <v>1012</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38">
         <v>2000</v>
       </c>
       <c r="M38">
@@ -3912,7 +3911,7 @@
         <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -3920,25 +3919,25 @@
         <v>107023</v>
       </c>
       <c r="B39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
-      </c>
-      <c r="D39" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="E39" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39">
         <v>3</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>153</v>
+      <c r="G39" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="I39">
         <v>30028</v>
@@ -3946,23 +3945,23 @@
       <c r="K39">
         <v>1012</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39">
         <v>30000</v>
       </c>
       <c r="M39">
         <v>1013</v>
       </c>
-      <c r="N39" s="7">
+      <c r="N39">
         <v>100</v>
       </c>
       <c r="O39">
         <v>1014</v>
       </c>
-      <c r="P39" s="7">
+      <c r="P39">
         <v>100</v>
       </c>
       <c r="Q39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -3979,13 +3978,13 @@
         <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="4">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>67</v>
@@ -3995,7 +3994,7 @@
       <c r="K40" s="4">
         <v>1002</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40">
         <v>5000</v>
       </c>
       <c r="M40" s="4"/>
@@ -4020,13 +4019,13 @@
         <v>59</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>67</v>
@@ -4038,7 +4037,7 @@
       <c r="K41" s="6">
         <v>1004</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41">
         <v>20000</v>
       </c>
       <c r="M41" s="6"/>
@@ -4063,13 +4062,13 @@
         <v>59</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F42" s="6">
         <v>3</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>67</v>
@@ -4081,7 +4080,7 @@
       <c r="K42" s="4">
         <v>1006</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42">
         <v>20000</v>
       </c>
       <c r="M42" s="6"/>
@@ -4106,13 +4105,13 @@
         <v>59</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F43" s="6">
         <v>4</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>67</v>
@@ -4124,7 +4123,7 @@
       <c r="K43" s="6">
         <v>1008</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43">
         <v>20000</v>
       </c>
       <c r="M43" s="6"/>
@@ -4143,19 +4142,19 @@
         <v>64</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F44" s="6">
         <v>5</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>67</v>
@@ -4167,7 +4166,7 @@
       <c r="K44" s="4">
         <v>1010</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44">
         <v>20000</v>
       </c>
       <c r="M44" s="6"/>
@@ -4183,22 +4182,22 @@
         <v>110006</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" s="6">
         <v>6</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>67</v>
@@ -4210,7 +4209,7 @@
       <c r="K45" s="6">
         <v>1012</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45">
         <v>20000</v>
       </c>
       <c r="M45" s="6"/>
@@ -4226,22 +4225,22 @@
         <v>110007</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F46" s="6">
         <v>7</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>67</v>
@@ -4253,7 +4252,7 @@
       <c r="K46" s="4">
         <v>1014</v>
       </c>
-      <c r="L46" s="10">
+      <c r="L46">
         <v>20000</v>
       </c>
       <c r="M46" s="6"/>
@@ -4278,13 +4277,13 @@
         <v>58</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>68</v>
@@ -4294,7 +4293,7 @@
       <c r="K47" s="6">
         <v>1002</v>
       </c>
-      <c r="L47" s="10">
+      <c r="L47">
         <v>5000</v>
       </c>
       <c r="M47" s="6"/>
@@ -4319,13 +4318,13 @@
         <v>58</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>79</v>
+      <c r="G48" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>68</v>
@@ -4337,7 +4336,7 @@
       <c r="K48" s="4">
         <v>1004</v>
       </c>
-      <c r="L48" s="10">
+      <c r="L48">
         <v>20000</v>
       </c>
       <c r="M48" s="4"/>
@@ -4362,13 +4361,13 @@
         <v>58</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>68</v>
@@ -4380,7 +4379,7 @@
       <c r="K49" s="6">
         <v>1006</v>
       </c>
-      <c r="L49" s="10">
+      <c r="L49">
         <v>20000</v>
       </c>
       <c r="M49" s="6"/>
@@ -4405,13 +4404,13 @@
         <v>58</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F50" s="4">
         <v>4</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>79</v>
+      <c r="G50" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>68</v>
@@ -4423,7 +4422,7 @@
       <c r="K50" s="4">
         <v>1008</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50">
         <v>20000</v>
       </c>
       <c r="M50" s="4"/>
@@ -4448,13 +4447,13 @@
         <v>58</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>68</v>
@@ -4466,7 +4465,7 @@
       <c r="K51" s="6">
         <v>1010</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51">
         <v>20000</v>
       </c>
       <c r="M51" s="6"/>
@@ -4482,22 +4481,22 @@
         <v>111006</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>58</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>68</v>
@@ -4509,7 +4508,7 @@
       <c r="K52" s="6">
         <v>1012</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52">
         <v>20000</v>
       </c>
       <c r="M52" s="6"/>
@@ -4525,22 +4524,22 @@
         <v>111007</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>58</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>68</v>
@@ -4552,7 +4551,7 @@
       <c r="K53" s="6">
         <v>1014</v>
       </c>
-      <c r="L53" s="10">
+      <c r="L53">
         <v>20000</v>
       </c>
       <c r="M53" s="6"/>
@@ -4564,39 +4563,31 @@
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A54" s="10">
+      <c r="A54">
         <v>112001</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" t="s">
         <v>178</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="E54" t="s">
         <v>179</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
         <v>180</v>
       </c>
-      <c r="F54" s="10">
-        <v>1</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10" t="s">
+      <c r="H54" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q54" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4605,25 +4596,25 @@
         <v>112002</v>
       </c>
       <c r="B55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
+        <v>178</v>
+      </c>
+      <c r="E55" t="s">
         <v>179</v>
-      </c>
-      <c r="E55" t="s">
-        <v>180</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I55">
         <v>30005</v>
@@ -4637,25 +4628,25 @@
         <v>112003</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D56" t="s">
+        <v>178</v>
+      </c>
+      <c r="E56" t="s">
         <v>179</v>
-      </c>
-      <c r="E56" t="s">
-        <v>180</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I56">
         <v>30010</v>
@@ -4669,25 +4660,25 @@
         <v>112004</v>
       </c>
       <c r="B57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D57" t="s">
+        <v>178</v>
+      </c>
+      <c r="E57" t="s">
         <v>179</v>
-      </c>
-      <c r="E57" t="s">
-        <v>180</v>
       </c>
       <c r="F57">
         <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I57">
         <v>30015</v>
@@ -4701,25 +4692,25 @@
         <v>112005</v>
       </c>
       <c r="B58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D58" t="s">
+        <v>178</v>
+      </c>
+      <c r="E58" t="s">
         <v>179</v>
-      </c>
-      <c r="E58" t="s">
-        <v>180</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I58">
         <v>30020</v>
@@ -4733,25 +4724,25 @@
         <v>112006</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D59" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" t="s">
         <v>179</v>
-      </c>
-      <c r="E59" t="s">
-        <v>180</v>
       </c>
       <c r="F59">
         <v>6</v>
       </c>
       <c r="G59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H59" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I59">
         <v>30025</v>
@@ -4765,25 +4756,25 @@
         <v>112007</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D60" t="s">
+        <v>178</v>
+      </c>
+      <c r="E60" t="s">
         <v>179</v>
-      </c>
-      <c r="E60" t="s">
-        <v>180</v>
       </c>
       <c r="F60">
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H60" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I60">
         <v>30030</v>
@@ -4797,34 +4788,34 @@
         <v>113001</v>
       </c>
       <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
         <v>182</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>183</v>
       </c>
-      <c r="D61" t="s">
-        <v>184</v>
-      </c>
       <c r="E61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H61" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K61">
         <v>1002</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61">
         <v>5000</v>
       </c>
       <c r="Q61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -4832,25 +4823,25 @@
         <v>113002</v>
       </c>
       <c r="B62" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" t="s">
         <v>192</v>
       </c>
-      <c r="C62" t="s">
-        <v>193</v>
-      </c>
       <c r="D62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E62" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H62" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J62" s="6">
         <v>2</v>
@@ -4858,11 +4849,11 @@
       <c r="K62">
         <v>1004</v>
       </c>
-      <c r="L62" s="10">
+      <c r="L62">
         <v>20000</v>
       </c>
       <c r="Q62" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
@@ -4870,25 +4861,25 @@
         <v>113003</v>
       </c>
       <c r="B63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" t="s">
         <v>194</v>
       </c>
-      <c r="C63" t="s">
-        <v>195</v>
-      </c>
       <c r="D63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J63" s="6">
         <v>3</v>
@@ -4896,11 +4887,11 @@
       <c r="K63">
         <v>1006</v>
       </c>
-      <c r="L63" s="10">
+      <c r="L63">
         <v>20000</v>
       </c>
       <c r="Q63" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
@@ -4908,25 +4899,25 @@
         <v>113004</v>
       </c>
       <c r="B64" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" t="s">
         <v>196</v>
       </c>
-      <c r="C64" t="s">
-        <v>197</v>
-      </c>
       <c r="D64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H64" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J64" s="6">
         <v>4</v>
@@ -4934,11 +4925,11 @@
       <c r="K64">
         <v>1008</v>
       </c>
-      <c r="L64" s="10">
+      <c r="L64">
         <v>20000</v>
       </c>
       <c r="Q64" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
@@ -4946,25 +4937,25 @@
         <v>113005</v>
       </c>
       <c r="B65" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" t="s">
         <v>198</v>
       </c>
-      <c r="C65" t="s">
-        <v>199</v>
-      </c>
       <c r="D65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J65" s="6">
         <v>5</v>
@@ -4972,11 +4963,11 @@
       <c r="K65">
         <v>1010</v>
       </c>
-      <c r="L65" s="10">
+      <c r="L65">
         <v>20000</v>
       </c>
       <c r="Q65" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
@@ -4984,25 +4975,25 @@
         <v>113006</v>
       </c>
       <c r="B66" t="s">
+        <v>199</v>
+      </c>
+      <c r="C66" t="s">
         <v>200</v>
       </c>
-      <c r="C66" t="s">
-        <v>201</v>
-      </c>
       <c r="D66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F66">
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J66" s="6">
         <v>6</v>
@@ -5010,11 +5001,11 @@
       <c r="K66">
         <v>1012</v>
       </c>
-      <c r="L66" s="10">
+      <c r="L66">
         <v>20000</v>
       </c>
       <c r="Q66" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.3">
@@ -5022,25 +5013,25 @@
         <v>113007</v>
       </c>
       <c r="B67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" t="s">
         <v>202</v>
       </c>
-      <c r="C67" t="s">
-        <v>203</v>
-      </c>
       <c r="D67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="H67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J67" s="6">
         <v>7</v>
@@ -5048,7 +5039,7 @@
       <c r="K67">
         <v>1014</v>
       </c>
-      <c r="L67" s="10">
+      <c r="L67">
         <v>20000</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1C4167-45DF-4D95-BC75-E4E23D49C7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6A4C39-E925-4A07-A035-28AB4210B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="795" windowWidth="21600" windowHeight="14685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="216">
   <si>
     <t>0,0</t>
   </si>
@@ -485,9 +485,6 @@
   <si>
     <t>engine_merger1</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_merger2</t>
   </si>
   <si>
     <t>engine_merger3</t>
@@ -924,139 +921,173 @@
     <t>거대 텅스텐 드릴을 작동하기 위한 모터 시설이다.</t>
   </si>
   <si>
+    <t>돌 드릴</t>
+  </si>
+  <si>
+    <t>철 드릴</t>
+  </si>
+  <si>
+    <t>금 드릴</t>
+  </si>
+  <si>
+    <t>흑요석 드릴</t>
+  </si>
+  <si>
+    <t>텅스텐 드릴</t>
+  </si>
+  <si>
+    <t>티타늄 드릴</t>
+  </si>
+  <si>
+    <t>engine_merger6</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>engine_merger7</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>drill1</t>
+  </si>
+  <si>
+    <t>Drill</t>
+  </si>
+  <si>
+    <t>drillIcon</t>
+  </si>
+  <si>
+    <t>DrillEntity</t>
+  </si>
+  <si>
+    <t>resource_merger1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceMerger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잉여 자원을 재활용하기 위한 시설이다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireCoreLevel</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory6</t>
+  </si>
+  <si>
+    <t>연구소 Lv.6</t>
+  </si>
+  <si>
+    <t>laboratory7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger2</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>resource_merger3</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>resource_merger4</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>resource_merger5</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger6</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>resource_merger7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>0,0;0,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>resourceMergerIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceMergerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EngineMergerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>거대 티타늄 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>돌 드릴</t>
-  </si>
-  <si>
-    <t>철 드릴</t>
-  </si>
-  <si>
-    <t>금 드릴</t>
-  </si>
-  <si>
-    <t>흑요석 드릴</t>
-  </si>
-  <si>
-    <t>텅스텐 드릴</t>
-  </si>
-  <si>
-    <t>티타늄 드릴</t>
-  </si>
-  <si>
-    <t>engine_merger6</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.6</t>
-  </si>
-  <si>
-    <t>engine_merger7</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.7</t>
-  </si>
-  <si>
-    <t>drill1</t>
-  </si>
-  <si>
-    <t>Drill</t>
-  </si>
-  <si>
-    <t>drillIcon</t>
-  </si>
-  <si>
-    <t>DrillEntity</t>
-  </si>
-  <si>
-    <t>resource_merger1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceMerger</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잉여 자원을 재활용하기 위한 시설이다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequireCoreLevel</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>laboratory6</t>
-  </si>
-  <si>
-    <t>연구소 Lv.6</t>
-  </si>
-  <si>
-    <t>laboratory7</t>
-  </si>
-  <si>
-    <t>연구소 Lv.7</t>
-  </si>
-  <si>
-    <t>연구소 Lv.5</t>
-  </si>
-  <si>
-    <t>resource_merger2</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.2</t>
-  </si>
-  <si>
-    <t>resource_merger3</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.3</t>
-  </si>
-  <si>
-    <t>resource_merger4</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.4</t>
-  </si>
-  <si>
-    <t>resource_merger5</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.5</t>
-  </si>
-  <si>
-    <t>resource_merger6</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.6</t>
-  </si>
-  <si>
-    <t>resource_merger7</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.7</t>
-  </si>
-  <si>
-    <t>0,0;0,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>resourceMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceMergerEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EngineMergerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1827,9 +1858,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:Q67" totalsRowShown="0">
-  <autoFilter ref="A1:Q67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
+  <autoFilter ref="A1:R67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
@@ -1847,6 +1878,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
+    <tableColumn id="17" xr3:uid="{E3C21EBB-36AF-43D2-B2EE-6134BD7B7912}" name="Length"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2115,7 +2147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.25" customWidth="1"/>
@@ -2129,9 +2161,11 @@
     <col min="11" max="11" width="27" customWidth="1"/>
     <col min="12" max="12" width="18.125" customWidth="1"/>
     <col min="13" max="13" width="17.75" customWidth="1"/>
+    <col min="17" max="17" width="15.625" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2145,22 +2179,22 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K1" t="s">
         <v>40</v>
@@ -2181,10 +2215,13 @@
         <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="R1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101011</v>
       </c>
@@ -2198,16 +2235,16 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K2">
         <v>1002</v>
@@ -2224,8 +2261,11 @@
       <c r="Q2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>101021</v>
       </c>
@@ -2239,16 +2279,16 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K3">
         <v>1002</v>
@@ -2271,8 +2311,11 @@
       <c r="Q3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>102011</v>
       </c>
@@ -2286,16 +2329,16 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4">
         <v>30001</v>
@@ -2315,8 +2358,11 @@
       <c r="Q4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>102012</v>
       </c>
@@ -2330,16 +2376,16 @@
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5">
         <v>30002</v>
@@ -2357,10 +2403,13 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>102013</v>
       </c>
@@ -2374,16 +2423,16 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6">
         <v>30003</v>
@@ -2401,10 +2450,13 @@
         <v>100</v>
       </c>
       <c r="Q6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>102021</v>
       </c>
@@ -2418,16 +2470,16 @@
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I7">
         <v>30001</v>
@@ -2453,8 +2505,11 @@
       <c r="Q7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>102022</v>
       </c>
@@ -2468,16 +2523,16 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I8">
         <v>30002</v>
@@ -2501,10 +2556,13 @@
         <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>102023</v>
       </c>
@@ -2518,16 +2576,16 @@
         <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I9">
         <v>30003</v>
@@ -2551,10 +2609,13 @@
         <v>100</v>
       </c>
       <c r="Q9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>103011</v>
       </c>
@@ -2568,16 +2629,16 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10">
         <v>30006</v>
@@ -2597,8 +2658,11 @@
       <c r="Q10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>103012</v>
       </c>
@@ -2612,16 +2676,16 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I11">
         <v>30007</v>
@@ -2639,10 +2703,13 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>103013</v>
       </c>
@@ -2656,16 +2723,16 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I12">
         <v>30008</v>
@@ -2683,10 +2750,13 @@
         <v>100</v>
       </c>
       <c r="Q12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>103021</v>
       </c>
@@ -2700,16 +2770,16 @@
         <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I13">
         <v>30006</v>
@@ -2735,8 +2805,11 @@
       <c r="Q13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>103022</v>
       </c>
@@ -2750,16 +2823,16 @@
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I14">
         <v>30007</v>
@@ -2783,10 +2856,13 @@
         <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>103023</v>
       </c>
@@ -2800,16 +2876,16 @@
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I15">
         <v>30008</v>
@@ -2833,33 +2909,36 @@
         <v>100</v>
       </c>
       <c r="Q15" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>104011</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I16">
         <v>30011</v>
@@ -2879,31 +2958,34 @@
       <c r="Q16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>104012</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I17">
         <v>30012</v>
@@ -2921,33 +3003,36 @@
         <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R17" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>104013</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I18">
         <v>30013</v>
@@ -2965,33 +3050,36 @@
         <v>100</v>
       </c>
       <c r="Q18" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>104021</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I19">
         <v>30011</v>
@@ -3017,31 +3105,34 @@
       <c r="Q19" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>104022</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I20">
         <v>30012</v>
@@ -3065,33 +3156,36 @@
         <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>104023</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F21">
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I21">
         <v>30013</v>
@@ -3115,33 +3209,36 @@
         <v>100</v>
       </c>
       <c r="Q21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>105011</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I22">
         <v>30016</v>
@@ -3161,31 +3258,34 @@
       <c r="Q22" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>105012</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I23">
         <v>30017</v>
@@ -3203,33 +3303,36 @@
         <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R23" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>105013</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I24">
         <v>30018</v>
@@ -3247,33 +3350,36 @@
         <v>100</v>
       </c>
       <c r="Q24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R24" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>105021</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I25">
         <v>30016</v>
@@ -3299,31 +3405,34 @@
       <c r="Q25" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R25" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>105022</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I26">
         <v>30017</v>
@@ -3347,33 +3456,36 @@
         <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R26" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>105023</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I27">
         <v>30018</v>
@@ -3397,33 +3509,36 @@
         <v>100</v>
       </c>
       <c r="Q27" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R27" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>106011</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I28">
         <v>30021</v>
@@ -3443,31 +3558,34 @@
       <c r="Q28" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>106012</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I29">
         <v>30022</v>
@@ -3485,33 +3603,36 @@
         <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>106013</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F30">
         <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I30">
         <v>30023</v>
@@ -3529,33 +3650,36 @@
         <v>100</v>
       </c>
       <c r="Q30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>106021</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I31">
         <v>30021</v>
@@ -3581,31 +3705,34 @@
       <c r="Q31" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R31" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>106022</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I32">
         <v>30022</v>
@@ -3629,33 +3756,36 @@
         <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R32" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>106023</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33">
         <v>30023</v>
@@ -3679,33 +3809,36 @@
         <v>100</v>
       </c>
       <c r="Q33" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>107011</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I34">
         <v>30026</v>
@@ -3725,31 +3858,34 @@
       <c r="Q34" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R34" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>107012</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I35">
         <v>30027</v>
@@ -3767,33 +3903,36 @@
         <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R35" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>107013</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36">
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I36">
         <v>30028</v>
@@ -3811,33 +3950,36 @@
         <v>100</v>
       </c>
       <c r="Q36" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R36" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>107021</v>
       </c>
       <c r="B37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I37">
         <v>30026</v>
@@ -3863,31 +4005,34 @@
       <c r="Q37" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R37" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>107022</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I38">
         <v>30027</v>
@@ -3911,33 +4056,36 @@
         <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R38" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>107023</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F39">
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I39">
         <v>30028</v>
@@ -3961,33 +4109,36 @@
         <v>100</v>
       </c>
       <c r="Q39" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="R39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>110001</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F40" s="4">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -4004,31 +4155,34 @@
       <c r="Q40" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R40" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>110002</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="6">
@@ -4047,31 +4201,34 @@
       <c r="Q41" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R41" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>110003</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F42" s="6">
         <v>3</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="6">
@@ -4090,31 +4247,34 @@
       <c r="Q42" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>110004</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F43" s="6">
         <v>4</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="6">
@@ -4133,31 +4293,34 @@
       <c r="Q43" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R43" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>110005</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" s="6">
         <v>5</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="6">
@@ -4176,31 +4339,34 @@
       <c r="Q44" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R44" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>110006</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F45" s="6">
         <v>6</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="6">
@@ -4219,31 +4385,34 @@
       <c r="Q45" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R45" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>110007</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F46" s="6">
         <v>7</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="6">
@@ -4262,8 +4431,11 @@
       <c r="Q46" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>111001</v>
       </c>
@@ -4271,22 +4443,22 @@
         <v>48</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
@@ -4303,31 +4475,34 @@
       <c r="Q47" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>111002</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>49</v>
+        <v>206</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="6">
@@ -4346,31 +4521,34 @@
       <c r="Q48" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R48" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>111003</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="6">
@@ -4389,31 +4567,34 @@
       <c r="Q49" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R49" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>111004</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F50" s="4">
         <v>4</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="6">
@@ -4432,31 +4613,34 @@
       <c r="Q50" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R50" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>111005</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="6">
@@ -4475,31 +4659,34 @@
       <c r="Q51" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R51" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>111006</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="6">
@@ -4518,31 +4705,34 @@
       <c r="Q52" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R52" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>111007</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="6">
@@ -4561,60 +4751,66 @@
       <c r="Q53" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>112001</v>
       </c>
       <c r="B54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" t="s">
         <v>177</v>
-      </c>
-      <c r="C54" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" t="s">
-        <v>178</v>
-      </c>
-      <c r="E54" t="s">
-        <v>179</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q54" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R54" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>112002</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D55" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I55">
         <v>30005</v>
@@ -4622,31 +4818,34 @@
       <c r="Q55" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R55" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>112003</v>
       </c>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E56" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I56">
         <v>30010</v>
@@ -4654,31 +4853,34 @@
       <c r="Q56" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R56" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>112004</v>
       </c>
       <c r="B57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D57" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F57">
         <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H57" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I57">
         <v>30015</v>
@@ -4686,31 +4888,34 @@
       <c r="Q57" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R57" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>112005</v>
       </c>
       <c r="B58" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D58" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H58" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I58">
         <v>30020</v>
@@ -4718,31 +4923,34 @@
       <c r="Q58" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>112006</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E59" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F59">
         <v>6</v>
       </c>
       <c r="G59" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I59">
         <v>30025</v>
@@ -4750,31 +4958,34 @@
       <c r="Q59" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>112007</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D60" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E60" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F60">
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H60" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="I60">
         <v>30030</v>
@@ -4782,31 +4993,34 @@
       <c r="Q60" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R60" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>113001</v>
       </c>
       <c r="B61" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" t="s">
         <v>181</v>
       </c>
-      <c r="C61" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" t="s">
-        <v>183</v>
-      </c>
       <c r="E61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H61" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K61">
         <v>1002</v>
@@ -4815,33 +5029,36 @@
         <v>5000</v>
       </c>
       <c r="Q61" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R61" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>113002</v>
       </c>
       <c r="B62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C62" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E62" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H62" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J62" s="6">
         <v>2</v>
@@ -4853,33 +5070,36 @@
         <v>20000</v>
       </c>
       <c r="Q62" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R62" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>113003</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C63" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E63" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H63" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J63" s="6">
         <v>3</v>
@@ -4891,33 +5111,36 @@
         <v>20000</v>
       </c>
       <c r="Q63" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R63" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>113004</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E64" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H64" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J64" s="6">
         <v>4</v>
@@ -4929,33 +5152,36 @@
         <v>20000</v>
       </c>
       <c r="Q64" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R64" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>113005</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H65" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J65" s="6">
         <v>5</v>
@@ -4967,33 +5193,36 @@
         <v>20000</v>
       </c>
       <c r="Q65" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R65" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>113006</v>
       </c>
       <c r="B66" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D66" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E66" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F66">
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H66" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J66" s="6">
         <v>6</v>
@@ -5005,33 +5234,36 @@
         <v>20000</v>
       </c>
       <c r="Q66" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="R66" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>113007</v>
       </c>
       <c r="B67" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H67" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J67" s="6">
         <v>7</v>
@@ -5041,6 +5273,12 @@
       </c>
       <c r="L67">
         <v>20000</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>201</v>
+      </c>
+      <c r="R67" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6A4C39-E925-4A07-A035-28AB4210B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="795" windowWidth="21600" windowHeight="14685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="795" windowWidth="21600" windowHeight="14685"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -20,12 +19,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -971,10 +970,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ResourceMerger</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>잉여 자원을 재활용하기 위한 시설이다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1042,14 +1037,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>resourceMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceMergerEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>EngineMergerEntity</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1088,13 +1075,25 @@
   </si>
   <si>
     <t>2,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceConverterEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>resourceConverterIcon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceConverter</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1858,27 +1857,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
-  <autoFilter ref="A1:R67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
+  <autoFilter ref="A1:R67"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Icon"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="EntityClassName"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Desc"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="RequireResearchId"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="RequireCoreLevel"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
-    <tableColumn id="17" xr3:uid="{E3C21EBB-36AF-43D2-B2EE-6134BD7B7912}" name="Length"/>
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="5" name="Name"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="8" name="Type"/>
+    <tableColumn id="14" name="Icon"/>
+    <tableColumn id="3" name="Level"/>
+    <tableColumn id="13" name="EntityClassName"/>
+    <tableColumn id="15" name="Desc"/>
+    <tableColumn id="16" name="RequireResearchId"/>
+    <tableColumn id="18" name="RequireCoreLevel"/>
+    <tableColumn id="11" name="BuildResourceId"/>
+    <tableColumn id="12" name="BuildResourceCount"/>
+    <tableColumn id="7" name="InputItemId"/>
+    <tableColumn id="10" name="InputItemCount"/>
+    <tableColumn id="6" name="OutputItemId"/>
+    <tableColumn id="9" name="OutputItemCount"/>
+    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="17" name="Length"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2146,7 +2145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2194,7 +2193,7 @@
         <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K1" t="s">
         <v>40</v>
@@ -2218,7 +2217,7 @@
         <v>64</v>
       </c>
       <c r="R1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -2262,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -2312,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -2359,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -2403,10 +2402,10 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -2450,10 +2449,10 @@
         <v>100</v>
       </c>
       <c r="Q6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -2506,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -2556,10 +2555,10 @@
         <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -2609,10 +2608,10 @@
         <v>100</v>
       </c>
       <c r="Q9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -2659,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -2703,10 +2702,10 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -2750,10 +2749,10 @@
         <v>100</v>
       </c>
       <c r="Q12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -2806,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -2856,10 +2855,10 @@
         <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -2909,10 +2908,10 @@
         <v>100</v>
       </c>
       <c r="Q15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -2959,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -3003,10 +3002,10 @@
         <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R17" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -3050,10 +3049,10 @@
         <v>100</v>
       </c>
       <c r="Q18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -3106,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -3156,10 +3155,10 @@
         <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R20" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -3209,10 +3208,10 @@
         <v>100</v>
       </c>
       <c r="Q21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -3259,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -3303,10 +3302,10 @@
         <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R23" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -3350,10 +3349,10 @@
         <v>100</v>
       </c>
       <c r="Q24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -3406,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -3456,10 +3455,10 @@
         <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R26" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -3509,10 +3508,10 @@
         <v>100</v>
       </c>
       <c r="Q27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -3559,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -3603,10 +3602,10 @@
         <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -3650,10 +3649,10 @@
         <v>100</v>
       </c>
       <c r="Q30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R30" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -3706,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -3756,10 +3755,10 @@
         <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R32" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -3809,10 +3808,10 @@
         <v>100</v>
       </c>
       <c r="Q33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R33" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -3859,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -3903,10 +3902,10 @@
         <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R35" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -3950,10 +3949,10 @@
         <v>100</v>
       </c>
       <c r="Q36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R36" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -4006,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -4056,10 +4055,10 @@
         <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R38" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -4109,10 +4108,10 @@
         <v>100</v>
       </c>
       <c r="Q39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R39" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -4156,7 +4155,7 @@
         <v>42</v>
       </c>
       <c r="R40" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -4202,7 +4201,7 @@
         <v>42</v>
       </c>
       <c r="R41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -4248,7 +4247,7 @@
         <v>42</v>
       </c>
       <c r="R42" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -4294,7 +4293,7 @@
         <v>42</v>
       </c>
       <c r="R43" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -4305,7 +4304,7 @@
         <v>63</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>58</v>
@@ -4340,7 +4339,7 @@
         <v>42</v>
       </c>
       <c r="R44" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -4348,10 +4347,10 @@
         <v>110006</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>58</v>
@@ -4386,7 +4385,7 @@
         <v>42</v>
       </c>
       <c r="R45" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -4394,10 +4393,10 @@
         <v>110007</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>58</v>
@@ -4432,7 +4431,7 @@
         <v>42</v>
       </c>
       <c r="R46" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -4455,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>67</v>
@@ -4476,7 +4475,7 @@
         <v>42</v>
       </c>
       <c r="R47" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -4484,7 +4483,7 @@
         <v>111002</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>53</v>
@@ -4499,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>67</v>
@@ -4522,7 +4521,7 @@
         <v>42</v>
       </c>
       <c r="R48" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -4545,7 +4544,7 @@
         <v>3</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>67</v>
@@ -4568,7 +4567,7 @@
         <v>42</v>
       </c>
       <c r="R49" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -4591,7 +4590,7 @@
         <v>4</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>67</v>
@@ -4614,7 +4613,7 @@
         <v>42</v>
       </c>
       <c r="R50" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -4637,7 +4636,7 @@
         <v>5</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>67</v>
@@ -4660,7 +4659,7 @@
         <v>42</v>
       </c>
       <c r="R51" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -4683,7 +4682,7 @@
         <v>6</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>67</v>
@@ -4706,7 +4705,7 @@
         <v>42</v>
       </c>
       <c r="R52" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -4729,7 +4728,7 @@
         <v>7</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>67</v>
@@ -4752,7 +4751,7 @@
         <v>42</v>
       </c>
       <c r="R53" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
@@ -4784,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -4819,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -4854,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -4889,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="R57" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -4924,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="R58" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -4959,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="R59" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -4985,7 +4984,7 @@
         <v>178</v>
       </c>
       <c r="H60" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I60">
         <v>30030</v>
@@ -4994,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="R60" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -5008,19 +5007,19 @@
         <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E61" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K61">
         <v>1002</v>
@@ -5029,10 +5028,10 @@
         <v>5000</v>
       </c>
       <c r="Q61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R61" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
@@ -5040,25 +5039,25 @@
         <v>113002</v>
       </c>
       <c r="B62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C62" t="s">
         <v>189</v>
       </c>
-      <c r="C62" t="s">
-        <v>190</v>
-      </c>
       <c r="D62" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J62" s="6">
         <v>2</v>
@@ -5070,10 +5069,10 @@
         <v>20000</v>
       </c>
       <c r="Q62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R62" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
@@ -5081,25 +5080,25 @@
         <v>113003</v>
       </c>
       <c r="B63" t="s">
+        <v>190</v>
+      </c>
+      <c r="C63" t="s">
         <v>191</v>
       </c>
-      <c r="C63" t="s">
-        <v>192</v>
-      </c>
       <c r="D63" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J63" s="6">
         <v>3</v>
@@ -5111,10 +5110,10 @@
         <v>20000</v>
       </c>
       <c r="Q63" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R63" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
@@ -5122,25 +5121,25 @@
         <v>113004</v>
       </c>
       <c r="B64" t="s">
+        <v>192</v>
+      </c>
+      <c r="C64" t="s">
         <v>193</v>
       </c>
-      <c r="C64" t="s">
-        <v>194</v>
-      </c>
       <c r="D64" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J64" s="6">
         <v>4</v>
@@ -5152,10 +5151,10 @@
         <v>20000</v>
       </c>
       <c r="Q64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R64" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -5163,25 +5162,25 @@
         <v>113005</v>
       </c>
       <c r="B65" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" t="s">
         <v>195</v>
       </c>
-      <c r="C65" t="s">
-        <v>196</v>
-      </c>
       <c r="D65" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H65" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J65" s="6">
         <v>5</v>
@@ -5193,10 +5192,10 @@
         <v>20000</v>
       </c>
       <c r="Q65" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R65" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
@@ -5204,25 +5203,25 @@
         <v>113006</v>
       </c>
       <c r="B66" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" t="s">
         <v>197</v>
       </c>
-      <c r="C66" t="s">
-        <v>198</v>
-      </c>
       <c r="D66" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F66">
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H66" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J66" s="6">
         <v>6</v>
@@ -5234,10 +5233,10 @@
         <v>20000</v>
       </c>
       <c r="Q66" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R66" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
@@ -5245,25 +5244,25 @@
         <v>113007</v>
       </c>
       <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
         <v>199</v>
       </c>
-      <c r="C67" t="s">
-        <v>200</v>
-      </c>
       <c r="D67" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H67" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J67" s="6">
         <v>7</v>
@@ -5275,10 +5274,10 @@
         <v>20000</v>
       </c>
       <c r="Q67" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R67" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468F5478-78DB-4502-B145-A771C363A6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="795" windowWidth="21600" windowHeight="14685"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -195,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -302,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="213">
   <si>
     <t>0,0</t>
   </si>
@@ -1029,14 +1030,6 @@
     <t>자원 합성기 Lv.7</t>
   </si>
   <si>
-    <t>0,0;0,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>EngineMergerEntity</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1063,17 +1056,6 @@
     <t>2,2</t>
   </si>
   <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>2,2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1088,12 +1070,19 @@
   <si>
     <t>ResourceConverter</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1857,27 +1846,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
-  <autoFilter ref="A1:R67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
+  <autoFilter ref="A1:R67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="5" name="Name"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="8" name="Type"/>
-    <tableColumn id="14" name="Icon"/>
-    <tableColumn id="3" name="Level"/>
-    <tableColumn id="13" name="EntityClassName"/>
-    <tableColumn id="15" name="Desc"/>
-    <tableColumn id="16" name="RequireResearchId"/>
-    <tableColumn id="18" name="RequireCoreLevel"/>
-    <tableColumn id="11" name="BuildResourceId"/>
-    <tableColumn id="12" name="BuildResourceCount"/>
-    <tableColumn id="7" name="InputItemId"/>
-    <tableColumn id="10" name="InputItemCount"/>
-    <tableColumn id="6" name="OutputItemId"/>
-    <tableColumn id="9" name="OutputItemCount"/>
-    <tableColumn id="4" name="Coordinates"/>
-    <tableColumn id="17" name="Length"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Icon"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="EntityClassName"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Desc"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="RequireResearchId"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="RequireCoreLevel"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Length"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2145,7 +2134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2217,7 +2206,7 @@
         <v>64</v>
       </c>
       <c r="R1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -2261,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -2311,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -2358,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -2402,10 +2391,10 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="R5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -2449,10 +2438,10 @@
         <v>100</v>
       </c>
       <c r="Q6" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="R6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -2505,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -2555,10 +2544,10 @@
         <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="R8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -2608,10 +2597,10 @@
         <v>100</v>
       </c>
       <c r="Q9" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="R9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -2658,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -2702,10 +2691,10 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="R11" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -2749,10 +2738,10 @@
         <v>100</v>
       </c>
       <c r="Q12" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -2805,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -2855,10 +2844,10 @@
         <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -2908,10 +2897,10 @@
         <v>100</v>
       </c>
       <c r="Q15" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -2958,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -3002,10 +2991,10 @@
         <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -3049,10 +3038,10 @@
         <v>100</v>
       </c>
       <c r="Q18" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -3105,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -3155,10 +3144,10 @@
         <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -3208,10 +3197,10 @@
         <v>100</v>
       </c>
       <c r="Q21" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -3258,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -3302,10 +3291,10 @@
         <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -3349,10 +3338,10 @@
         <v>100</v>
       </c>
       <c r="Q24" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -3405,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -3455,10 +3444,10 @@
         <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -3508,10 +3497,10 @@
         <v>100</v>
       </c>
       <c r="Q27" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -3558,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -3602,10 +3591,10 @@
         <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -3649,10 +3638,10 @@
         <v>100</v>
       </c>
       <c r="Q30" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -3705,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -3755,10 +3744,10 @@
         <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -3808,10 +3797,10 @@
         <v>100</v>
       </c>
       <c r="Q33" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -3858,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -3902,10 +3891,10 @@
         <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -3949,10 +3938,10 @@
         <v>100</v>
       </c>
       <c r="Q36" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -4005,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -4055,10 +4044,10 @@
         <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -4108,10 +4097,10 @@
         <v>100</v>
       </c>
       <c r="Q39" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -4155,7 +4144,7 @@
         <v>42</v>
       </c>
       <c r="R40" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -4201,7 +4190,7 @@
         <v>42</v>
       </c>
       <c r="R41" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -4247,7 +4236,7 @@
         <v>42</v>
       </c>
       <c r="R42" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -4293,7 +4282,7 @@
         <v>42</v>
       </c>
       <c r="R43" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -4339,7 +4328,7 @@
         <v>42</v>
       </c>
       <c r="R44" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -4385,7 +4374,7 @@
         <v>42</v>
       </c>
       <c r="R45" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -4431,7 +4420,7 @@
         <v>42</v>
       </c>
       <c r="R46" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -4454,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>67</v>
@@ -4475,7 +4464,7 @@
         <v>42</v>
       </c>
       <c r="R47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -4483,7 +4472,7 @@
         <v>111002</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>53</v>
@@ -4498,7 +4487,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>67</v>
@@ -4521,7 +4510,7 @@
         <v>42</v>
       </c>
       <c r="R48" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -4544,7 +4533,7 @@
         <v>3</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>67</v>
@@ -4567,7 +4556,7 @@
         <v>42</v>
       </c>
       <c r="R49" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -4590,7 +4579,7 @@
         <v>4</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>67</v>
@@ -4613,7 +4602,7 @@
         <v>42</v>
       </c>
       <c r="R50" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -4636,7 +4625,7 @@
         <v>5</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>67</v>
@@ -4659,7 +4648,7 @@
         <v>42</v>
       </c>
       <c r="R51" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -4682,7 +4671,7 @@
         <v>6</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>67</v>
@@ -4705,7 +4694,7 @@
         <v>42</v>
       </c>
       <c r="R52" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -4728,7 +4717,7 @@
         <v>7</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>67</v>
@@ -4751,7 +4740,7 @@
         <v>42</v>
       </c>
       <c r="R53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
@@ -4783,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -4818,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -4853,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -4888,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="R57" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -4923,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="R58" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -4958,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="R59" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -4984,7 +4973,7 @@
         <v>178</v>
       </c>
       <c r="H60" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I60">
         <v>30030</v>
@@ -4993,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="R60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -5007,16 +4996,16 @@
         <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E61" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>181</v>
@@ -5027,11 +5016,11 @@
       <c r="L61">
         <v>5000</v>
       </c>
-      <c r="Q61" t="s">
-        <v>200</v>
+      <c r="Q61" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="R61" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
@@ -5045,16 +5034,16 @@
         <v>189</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E62" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H62" t="s">
         <v>181</v>
@@ -5068,11 +5057,11 @@
       <c r="L62">
         <v>20000</v>
       </c>
-      <c r="Q62" t="s">
-        <v>200</v>
+      <c r="Q62" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="R62" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
@@ -5086,16 +5075,16 @@
         <v>191</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E63" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H63" t="s">
         <v>181</v>
@@ -5109,11 +5098,11 @@
       <c r="L63">
         <v>20000</v>
       </c>
-      <c r="Q63" t="s">
-        <v>200</v>
+      <c r="Q63" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="R63" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
@@ -5127,16 +5116,16 @@
         <v>193</v>
       </c>
       <c r="D64" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E64" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H64" t="s">
         <v>181</v>
@@ -5150,11 +5139,11 @@
       <c r="L64">
         <v>20000</v>
       </c>
-      <c r="Q64" t="s">
-        <v>200</v>
+      <c r="Q64" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="R64" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -5168,16 +5157,16 @@
         <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E65" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H65" t="s">
         <v>181</v>
@@ -5191,11 +5180,11 @@
       <c r="L65">
         <v>20000</v>
       </c>
-      <c r="Q65" t="s">
-        <v>200</v>
+      <c r="Q65" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="R65" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
@@ -5209,16 +5198,16 @@
         <v>197</v>
       </c>
       <c r="D66" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E66" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F66">
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H66" t="s">
         <v>181</v>
@@ -5232,11 +5221,11 @@
       <c r="L66">
         <v>20000</v>
       </c>
-      <c r="Q66" t="s">
-        <v>200</v>
+      <c r="Q66" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="R66" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
@@ -5250,16 +5239,16 @@
         <v>199</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E67" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H67" t="s">
         <v>181</v>
@@ -5273,11 +5262,11 @@
       <c r="L67">
         <v>20000</v>
       </c>
-      <c r="Q67" t="s">
-        <v>200</v>
+      <c r="Q67" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="R67" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468F5478-78DB-4502-B145-A771C363A6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Facility_Data" sheetId="1" r:id="rId1"/>
@@ -20,12 +19,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>HOME2</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -303,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="199">
   <si>
     <t>0,0</t>
   </si>
@@ -475,614 +474,538 @@
     <t>연구소 Lv.4</t>
   </si>
   <si>
+    <t>stone_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger3</t>
+  </si>
+  <si>
+    <t>engine_merger4</t>
+  </si>
+  <si>
+    <t>engine_merger5</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>EngineMerger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laboratory</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory2</t>
+  </si>
+  <si>
+    <t>laboratory3</t>
+  </si>
+  <si>
+    <t>laboratory4</t>
+  </si>
+  <si>
+    <t>laboratory5</t>
+  </si>
+  <si>
+    <t>Coordinates</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구를 진행하여 공장을 강화할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 엔진을 개발하거나, 기존의 엔진들을 합성할 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityClassName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LabEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProcessEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireResearchId</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>gold_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>obsidian_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner2</t>
+  </si>
+  <si>
+    <t>obsidian_miner3</t>
+  </si>
+  <si>
+    <t>obsidian_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor2</t>
+  </si>
+  <si>
+    <t>obsidian_processor3</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>tunstein_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner2</t>
+  </si>
+  <si>
+    <t>gold_miner3</t>
+  </si>
+  <si>
+    <t>gold_processor2</t>
+  </si>
+  <si>
+    <t>gold_processor3</t>
+  </si>
+  <si>
+    <t>tunstein_miner2</t>
+  </si>
+  <si>
+    <t>tunstein_miner3</t>
+  </si>
+  <si>
+    <t>tunstein_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_processor2</t>
+  </si>
+  <si>
+    <t>tunstein_processor3</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>titanium_miner1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor2</t>
+  </si>
+  <si>
+    <t>titanium_processor3</t>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 드릴</t>
+  </si>
+  <si>
+    <t>거대 구리 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>drill2</t>
+  </si>
+  <si>
+    <t>drill3</t>
+  </si>
+  <si>
+    <t>drill4</t>
+  </si>
+  <si>
+    <t>drill5</t>
+  </si>
+  <si>
+    <t>drill6</t>
+  </si>
+  <si>
+    <t>drill7</t>
+  </si>
+  <si>
+    <t>거대 돌 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 철 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 금 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 흑요석 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>거대 텅스텐 드릴을 작동하기 위한 모터 시설이다.</t>
+  </si>
+  <si>
+    <t>돌 드릴</t>
+  </si>
+  <si>
+    <t>철 드릴</t>
+  </si>
+  <si>
+    <t>금 드릴</t>
+  </si>
+  <si>
+    <t>흑요석 드릴</t>
+  </si>
+  <si>
+    <t>텅스텐 드릴</t>
+  </si>
+  <si>
+    <t>티타늄 드릴</t>
+  </si>
+  <si>
+    <t>engine_merger6</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>engine_merger7</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>drill1</t>
+  </si>
+  <si>
+    <t>Drill</t>
+  </si>
+  <si>
+    <t>DrillEntity</t>
+  </si>
+  <si>
+    <t>resource_merger1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잉여 자원을 재활용하기 위한 시설이다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireCoreLevel</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory6</t>
+  </si>
+  <si>
+    <t>연구소 Lv.6</t>
+  </si>
+  <si>
+    <t>laboratory7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger2</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>resource_merger3</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>resource_merger4</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>resource_merger5</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger6</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>resource_merger7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>EngineMergerEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대 티타늄 드릴을 작동하기 위한 모터 시설이다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceConverterEntity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceConverter</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1</t>
+  </si>
+  <si>
     <t>stone_miner1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>stone_processor1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_merger1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_merger3</t>
-  </si>
-  <si>
-    <t>engine_merger4</t>
-  </si>
-  <si>
-    <t>engine_merger5</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.2</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.3</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.4</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.5</t>
-  </si>
-  <si>
-    <t>EngineMerger</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Laboratory</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>laboratory1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>laboratory2</t>
-  </si>
-  <si>
-    <t>laboratory3</t>
-  </si>
-  <si>
-    <t>laboratory4</t>
-  </si>
-  <si>
-    <t>laboratory5</t>
-  </si>
-  <si>
-    <t>Coordinates</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구를 진행하여 공장을 강화할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>새로운 엔진을 개발하거나, 기존의 엔진들을 합성할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 광석을 철 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 광석을 돌 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 광석을 구리 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EntityClassName</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MinerEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LabEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProcessEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>labIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>labIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequireResearchId</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>금 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>gold_miner1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>gold_processor1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>금 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>obsidian_miner1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>obsidian_miner2</t>
-  </si>
-  <si>
-    <t>obsidian_miner3</t>
-  </si>
-  <si>
-    <t>obsidian_processor1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>obsidian_processor2</t>
-  </si>
-  <si>
-    <t>obsidian_processor3</t>
-  </si>
-  <si>
-    <t>금 가공 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 채굴 시설 Lv.2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 채굴 시설 Lv.3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 가공 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>흑요석 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>금 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>tunstein_miner1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>gold_miner2</t>
-  </si>
-  <si>
-    <t>gold_miner3</t>
-  </si>
-  <si>
-    <t>gold_processor2</t>
-  </si>
-  <si>
-    <t>gold_processor3</t>
-  </si>
-  <si>
-    <t>tunstein_miner2</t>
-  </si>
-  <si>
-    <t>tunstein_miner3</t>
-  </si>
-  <si>
-    <t>tunstein_processor1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>tunstein_processor2</t>
-  </si>
-  <si>
-    <t>tunstein_processor3</t>
-  </si>
-  <si>
-    <t>텅스텐 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>텅스텐 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>텅스텐 가공 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>텅스텐 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>텅스텐 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 광석을 텅스텐 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 광석을 흑요석 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 광석을 금 자재로 가공할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_miner1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_miner2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_miner3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_processor1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_processor2</t>
-  </si>
-  <si>
-    <t>titanium_processor3</t>
-  </si>
-  <si>
-    <t>티타늄 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>티타늄 가공 시설 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>티타늄 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>티타늄 채굴 시설 Lv.3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 광석을 생산할 수 있다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>티타늄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 광석을 티타늄 자재로 가공할 수 있다.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 드릴</t>
-  </si>
-  <si>
-    <t>거대 구리 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>drill2</t>
-  </si>
-  <si>
-    <t>drill3</t>
-  </si>
-  <si>
-    <t>drill4</t>
-  </si>
-  <si>
-    <t>drill5</t>
-  </si>
-  <si>
-    <t>drill6</t>
-  </si>
-  <si>
-    <t>drill7</t>
-  </si>
-  <si>
-    <t>거대 돌 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>거대 철 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>거대 금 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>거대 흑요석 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>거대 텅스텐 드릴을 작동하기 위한 모터 시설이다.</t>
-  </si>
-  <si>
-    <t>돌 드릴</t>
-  </si>
-  <si>
-    <t>철 드릴</t>
-  </si>
-  <si>
-    <t>금 드릴</t>
-  </si>
-  <si>
-    <t>흑요석 드릴</t>
-  </si>
-  <si>
-    <t>텅스텐 드릴</t>
-  </si>
-  <si>
-    <t>티타늄 드릴</t>
-  </si>
-  <si>
-    <t>engine_merger6</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.6</t>
-  </si>
-  <si>
-    <t>engine_merger7</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.7</t>
-  </si>
-  <si>
-    <t>drill1</t>
-  </si>
-  <si>
-    <t>Drill</t>
-  </si>
-  <si>
-    <t>drillIcon</t>
-  </si>
-  <si>
-    <t>DrillEntity</t>
-  </si>
-  <si>
-    <t>resource_merger1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잉여 자원을 재활용하기 위한 시설이다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequireCoreLevel</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>laboratory6</t>
-  </si>
-  <si>
-    <t>연구소 Lv.6</t>
-  </si>
-  <si>
-    <t>laboratory7</t>
-  </si>
-  <si>
-    <t>연구소 Lv.7</t>
-  </si>
-  <si>
-    <t>연구소 Lv.5</t>
-  </si>
-  <si>
-    <t>resource_merger2</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.2</t>
-  </si>
-  <si>
-    <t>resource_merger3</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.3</t>
-  </si>
-  <si>
-    <t>resource_merger4</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.4</t>
-  </si>
-  <si>
-    <t>resource_merger5</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.5</t>
-  </si>
-  <si>
-    <t>resource_merger6</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.6</t>
-  </si>
-  <si>
-    <t>resource_merger7</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.7</t>
-  </si>
-  <si>
-    <t>EngineMergerEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_merger2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>거대 티타늄 드릴을 작동하기 위한 모터 시설이다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Length</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1</t>
-  </si>
-  <si>
-    <t>1,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>2,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceConverterEntity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>resourceConverterIcon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceConverter</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0;1,1</t>
+    <t>stone_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>drill</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_merger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1467,7 +1390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1619,17 +1542,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1759,7 +1671,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1779,9 +1691,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1846,27 +1755,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
-  <autoFilter ref="A1:R67" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:R67" totalsRowShown="0">
+  <autoFilter ref="A1:R67"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Type"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Icon"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="EntityClassName"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Desc"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="RequireResearchId"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="RequireCoreLevel"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="BuildResourceId"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="BuildResourceCount"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="InputItemId"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="InputItemCount"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="OutputItemId"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OutputItemCount"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Length"/>
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="5" name="Name"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="8" name="Type"/>
+    <tableColumn id="14" name="Icon"/>
+    <tableColumn id="3" name="Level"/>
+    <tableColumn id="13" name="EntityClassName"/>
+    <tableColumn id="15" name="Desc"/>
+    <tableColumn id="16" name="RequireResearchId"/>
+    <tableColumn id="18" name="RequireCoreLevel"/>
+    <tableColumn id="11" name="BuildResourceId"/>
+    <tableColumn id="12" name="BuildResourceCount"/>
+    <tableColumn id="7" name="InputItemId"/>
+    <tableColumn id="10" name="InputItemCount"/>
+    <tableColumn id="6" name="OutputItemId"/>
+    <tableColumn id="9" name="OutputItemCount"/>
+    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="17" name="Length"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2134,7 +2043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2167,22 +2076,22 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="J1" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="K1" t="s">
         <v>40</v>
@@ -2203,10 +2112,10 @@
         <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R1" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -2214,7 +2123,7 @@
         <v>101011</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -2222,17 +2131,14 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>82</v>
+      <c r="E2" t="s">
+        <v>181</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K2">
         <v>1002</v>
@@ -2250,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -2258,7 +2164,7 @@
         <v>101021</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -2266,17 +2172,14 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>83</v>
+      <c r="E3" t="s">
+        <v>182</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K3">
         <v>1002</v>
@@ -2300,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -2316,17 +2219,14 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>84</v>
+      <c r="E4" t="s">
+        <v>183</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I4">
         <v>30001</v>
@@ -2347,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -2363,17 +2263,14 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>82</v>
+      <c r="E5" t="s">
+        <v>183</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I5">
         <v>30002</v>
@@ -2391,10 +2288,10 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="R5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -2410,17 +2307,14 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>85</v>
+      <c r="E6" t="s">
+        <v>183</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I6">
         <v>30003</v>
@@ -2438,10 +2332,10 @@
         <v>100</v>
       </c>
       <c r="Q6" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="R6" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -2457,17 +2351,14 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>86</v>
+      <c r="E7" t="s">
+        <v>184</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I7">
         <v>30001</v>
@@ -2494,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -2510,17 +2401,14 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>84</v>
+      <c r="E8" t="s">
+        <v>184</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I8">
         <v>30002</v>
@@ -2544,10 +2432,10 @@
         <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="R8" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -2563,17 +2451,14 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>86</v>
+      <c r="E9" t="s">
+        <v>184</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I9">
         <v>30003</v>
@@ -2597,10 +2482,10 @@
         <v>100</v>
       </c>
       <c r="Q9" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="R9" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -2616,16 +2501,13 @@
       <c r="D10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>87</v>
+      <c r="E10" t="s">
+        <v>185</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" t="s">
         <v>68</v>
       </c>
       <c r="I10">
@@ -2647,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -2663,16 +2545,13 @@
       <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>87</v>
+      <c r="E11" t="s">
+        <v>185</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" t="s">
         <v>68</v>
       </c>
       <c r="I11">
@@ -2691,10 +2570,10 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="R11" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -2710,16 +2589,13 @@
       <c r="D12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>87</v>
+      <c r="E12" t="s">
+        <v>185</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" t="s">
         <v>68</v>
       </c>
       <c r="I12">
@@ -2741,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -2757,17 +2633,14 @@
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>87</v>
+      <c r="E13" t="s">
+        <v>186</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I13">
         <v>30006</v>
@@ -2794,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -2810,17 +2683,14 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>87</v>
+      <c r="E14" t="s">
+        <v>186</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>30007</v>
@@ -2847,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -2863,17 +2733,14 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>87</v>
+      <c r="E15" t="s">
+        <v>186</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I15">
         <v>30008</v>
@@ -2900,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -2908,25 +2775,22 @@
         <v>104011</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>82</v>
+      <c r="E16" t="s">
+        <v>187</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="I16">
         <v>30011</v>
@@ -2947,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -2955,25 +2819,22 @@
         <v>104012</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>82</v>
+      <c r="E17" t="s">
+        <v>187</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="I17">
         <v>30012</v>
@@ -2994,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -3002,25 +2863,22 @@
         <v>104013</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>82</v>
+      <c r="E18" t="s">
+        <v>187</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="I18">
         <v>30013</v>
@@ -3041,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -3049,25 +2907,22 @@
         <v>104021</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>82</v>
+      <c r="E19" t="s">
+        <v>188</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="I19">
         <v>30011</v>
@@ -3094,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -3102,25 +2957,22 @@
         <v>104022</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>82</v>
+      <c r="E20" t="s">
+        <v>188</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="I20">
         <v>30012</v>
@@ -3147,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -3155,25 +3007,22 @@
         <v>104023</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>82</v>
+      <c r="E21" t="s">
+        <v>188</v>
       </c>
       <c r="F21">
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="I21">
         <v>30013</v>
@@ -3200,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -3208,25 +3057,22 @@
         <v>105011</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>82</v>
+      <c r="E22" t="s">
+        <v>189</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="I22">
         <v>30016</v>
@@ -3247,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -3255,25 +3101,22 @@
         <v>105012</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>82</v>
+      <c r="E23" t="s">
+        <v>189</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="I23">
         <v>30017</v>
@@ -3294,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -3302,25 +3145,22 @@
         <v>105013</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>82</v>
+      <c r="E24" t="s">
+        <v>189</v>
       </c>
       <c r="F24">
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H24" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="I24">
         <v>30018</v>
@@ -3341,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -3349,25 +3189,22 @@
         <v>105021</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>82</v>
+      <c r="E25" t="s">
+        <v>190</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="I25">
         <v>30016</v>
@@ -3394,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -3402,25 +3239,22 @@
         <v>105022</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>82</v>
+      <c r="E26" t="s">
+        <v>190</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="I26">
         <v>30017</v>
@@ -3447,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -3455,25 +3289,22 @@
         <v>105023</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>82</v>
+      <c r="E27" t="s">
+        <v>190</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="I27">
         <v>30018</v>
@@ -3500,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -3508,25 +3339,22 @@
         <v>106011</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>82</v>
+      <c r="E28" t="s">
+        <v>191</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="I28">
         <v>30021</v>
@@ -3547,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -3555,25 +3383,22 @@
         <v>106012</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>82</v>
+      <c r="E29" t="s">
+        <v>191</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
-      </c>
-      <c r="H29" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="I29">
         <v>30022</v>
@@ -3594,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -3602,25 +3427,22 @@
         <v>106013</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>82</v>
+      <c r="E30" t="s">
+        <v>191</v>
       </c>
       <c r="F30">
         <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
-      </c>
-      <c r="H30" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="I30">
         <v>30023</v>
@@ -3641,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -3649,25 +3471,22 @@
         <v>106021</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>82</v>
+      <c r="E31" t="s">
+        <v>192</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
-      </c>
-      <c r="H31" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="I31">
         <v>30021</v>
@@ -3694,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -3702,25 +3521,22 @@
         <v>106022</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
+      <c r="E32" t="s">
+        <v>192</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="I32">
         <v>30022</v>
@@ -3747,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -3755,25 +3571,22 @@
         <v>106023</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>82</v>
+      <c r="E33" t="s">
+        <v>192</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
-      </c>
-      <c r="H33" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="I33">
         <v>30023</v>
@@ -3800,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -3808,25 +3621,22 @@
         <v>107011</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>82</v>
+      <c r="E34" t="s">
+        <v>193</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H34" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="I34">
         <v>30026</v>
@@ -3847,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -3855,25 +3665,22 @@
         <v>107012</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>82</v>
+      <c r="E35" t="s">
+        <v>193</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>78</v>
-      </c>
-      <c r="H35" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="I35">
         <v>30027</v>
@@ -3894,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -3902,25 +3709,22 @@
         <v>107013</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>82</v>
+      <c r="E36" t="s">
+        <v>193</v>
       </c>
       <c r="F36">
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>78</v>
-      </c>
-      <c r="H36" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="I36">
         <v>30028</v>
@@ -3941,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -3949,26 +3753,24 @@
         <v>107021</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>82</v>
+      <c r="E37" t="s">
+        <v>194</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>151</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H37" s="7"/>
       <c r="I37">
         <v>30026</v>
       </c>
@@ -3994,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -4002,26 +3804,24 @@
         <v>107022</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>82</v>
+      <c r="E38" t="s">
+        <v>194</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>151</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H38" s="7"/>
       <c r="I38">
         <v>30027</v>
       </c>
@@ -4047,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -4055,26 +3855,24 @@
         <v>107023</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>82</v>
+      <c r="E39" t="s">
+        <v>194</v>
       </c>
       <c r="F39">
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>151</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H39" s="7"/>
       <c r="I39">
         <v>30028</v>
       </c>
@@ -4100,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -4108,25 +3906,25 @@
         <v>110001</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>89</v>
+        <v>57</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F40" s="4">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -4144,7 +3942,7 @@
         <v>42</v>
       </c>
       <c r="R40" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -4152,25 +3950,25 @@
         <v>110002</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="6">
@@ -4190,7 +3988,7 @@
         <v>42</v>
       </c>
       <c r="R41" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -4198,25 +3996,25 @@
         <v>110003</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F42" s="6">
         <v>3</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="6">
@@ -4236,7 +4034,7 @@
         <v>42</v>
       </c>
       <c r="R42" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -4244,25 +4042,25 @@
         <v>110004</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F43" s="6">
         <v>4</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="6">
@@ -4282,7 +4080,7 @@
         <v>42</v>
       </c>
       <c r="R43" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -4290,25 +4088,25 @@
         <v>110005</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F44" s="6">
         <v>5</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="6">
@@ -4328,7 +4126,7 @@
         <v>42</v>
       </c>
       <c r="R44" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -4336,25 +4134,25 @@
         <v>110006</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F45" s="6">
         <v>6</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="6">
@@ -4374,7 +4172,7 @@
         <v>42</v>
       </c>
       <c r="R45" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -4382,25 +4180,25 @@
         <v>110007</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="F46" s="6">
         <v>7</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="6">
@@ -4420,7 +4218,7 @@
         <v>42</v>
       </c>
       <c r="R46" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -4428,25 +4226,25 @@
         <v>111001</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>90</v>
+        <v>56</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
@@ -4464,7 +4262,7 @@
         <v>42</v>
       </c>
       <c r="R47" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -4472,25 +4270,25 @@
         <v>111002</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="6">
@@ -4510,7 +4308,7 @@
         <v>42</v>
       </c>
       <c r="R48" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -4518,25 +4316,25 @@
         <v>111003</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>91</v>
+        <v>56</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="6">
@@ -4556,7 +4354,7 @@
         <v>42</v>
       </c>
       <c r="R49" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -4564,25 +4362,25 @@
         <v>111004</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F50" s="4">
         <v>4</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="6">
@@ -4602,7 +4400,7 @@
         <v>42</v>
       </c>
       <c r="R50" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -4610,25 +4408,25 @@
         <v>111005</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>91</v>
+      <c r="E51" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F51" s="6">
         <v>5</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="6">
@@ -4648,7 +4446,7 @@
         <v>42</v>
       </c>
       <c r="R51" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -4656,25 +4454,25 @@
         <v>111006</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>90</v>
+        <v>56</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F52" s="6">
         <v>6</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="6">
@@ -4694,7 +4492,7 @@
         <v>42</v>
       </c>
       <c r="R52" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -4702,25 +4500,25 @@
         <v>111007</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>90</v>
+        <v>56</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F53" s="6">
         <v>7</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="6">
@@ -4740,7 +4538,7 @@
         <v>42</v>
       </c>
       <c r="R53" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
@@ -4748,31 +4546,31 @@
         <v>112001</v>
       </c>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="D54" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H54" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="Q54" t="s">
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
@@ -4780,25 +4578,25 @@
         <v>112002</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H55" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I55">
         <v>30005</v>
@@ -4807,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -4815,25 +4613,25 @@
         <v>112003</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="C56" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H56" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I56">
         <v>30010</v>
@@ -4842,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -4850,25 +4648,25 @@
         <v>112004</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F57">
         <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H57" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="I57">
         <v>30015</v>
@@ -4877,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="R57" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -4885,25 +4683,25 @@
         <v>112005</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E58" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H58" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="I58">
         <v>30020</v>
@@ -4912,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="R58" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -4920,25 +4718,25 @@
         <v>112006</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F59">
         <v>6</v>
       </c>
       <c r="G59" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H59" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="I59">
         <v>30025</v>
@@ -4947,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="R59" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -4955,25 +4753,25 @@
         <v>112007</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="D60" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F60">
         <v>7</v>
       </c>
       <c r="G60" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="H60" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I60">
         <v>30030</v>
@@ -4982,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="R60" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
@@ -4990,25 +4788,25 @@
         <v>113001</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="D61" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E61" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H61" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="K61">
         <v>1002</v>
@@ -5020,7 +4818,7 @@
         <v>42</v>
       </c>
       <c r="R61" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
@@ -5028,25 +4826,25 @@
         <v>113002</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="C62" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="D62" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E62" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H62" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J62" s="6">
         <v>2</v>
@@ -5061,7 +4859,7 @@
         <v>42</v>
       </c>
       <c r="R62" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
@@ -5069,25 +4867,25 @@
         <v>113003</v>
       </c>
       <c r="B63" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D63" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E63" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H63" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J63" s="6">
         <v>3</v>
@@ -5099,10 +4897,10 @@
         <v>20000</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="R63" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
@@ -5110,25 +4908,25 @@
         <v>113004</v>
       </c>
       <c r="B64" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="C64" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="D64" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E64" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F64">
         <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H64" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J64" s="6">
         <v>4</v>
@@ -5140,10 +4938,10 @@
         <v>20000</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="R64" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
@@ -5151,25 +4949,25 @@
         <v>113005</v>
       </c>
       <c r="B65" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="C65" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="D65" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E65" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H65" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J65" s="6">
         <v>5</v>
@@ -5181,10 +4979,10 @@
         <v>20000</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="R65" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
@@ -5192,25 +4990,25 @@
         <v>113006</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="D66" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E66" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F66">
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H66" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J66" s="6">
         <v>6</v>
@@ -5222,10 +5020,10 @@
         <v>20000</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="R66" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
@@ -5233,25 +5031,25 @@
         <v>113007</v>
       </c>
       <c r="B67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" t="s">
+        <v>177</v>
+      </c>
+      <c r="E67" t="s">
         <v>198</v>
-      </c>
-      <c r="C67" t="s">
-        <v>199</v>
-      </c>
-      <c r="D67" t="s">
-        <v>210</v>
-      </c>
-      <c r="E67" t="s">
-        <v>209</v>
       </c>
       <c r="F67">
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H67" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J67" s="6">
         <v>7</v>
@@ -5263,10 +5061,10 @@
         <v>20000</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="R67" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Facility_Data.xlsx
@@ -2144,7 +2144,7 @@
         <v>1002</v>
       </c>
       <c r="L2">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="O2">
         <v>1001</v>
@@ -2185,7 +2185,7 @@
         <v>1002</v>
       </c>
       <c r="L3">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="M3">
         <v>1001</v>
